--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129894004</v>
+        <v>129893993</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447553</v>
+        <v>447392</v>
       </c>
       <c r="R6" t="n">
-        <v>6804480</v>
+        <v>6804569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893993</v>
+        <v>129894004</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447392</v>
+        <v>447553</v>
       </c>
       <c r="R7" t="n">
-        <v>6804569</v>
+        <v>6804480</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -3050,54 +3050,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893960</v>
+        <v>129893905</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447591</v>
+        <v>447582</v>
       </c>
       <c r="R26" t="n">
-        <v>6804697</v>
+        <v>6804515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3138,7 +3129,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3157,45 +3147,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893905</v>
+        <v>129893960</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447582</v>
+        <v>447591</v>
       </c>
       <c r="R27" t="n">
-        <v>6804515</v>
+        <v>6804697</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3236,6 +3235,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3254,45 +3254,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893902</v>
+        <v>129893957</v>
       </c>
       <c r="B28" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447430</v>
+        <v>447418</v>
       </c>
       <c r="R28" t="n">
-        <v>6804548</v>
+        <v>6804561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,6 +3342,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3351,7 +3361,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893903</v>
+        <v>129893902</v>
       </c>
       <c r="B29" t="n">
         <v>79700</v>
@@ -3386,10 +3396,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447486</v>
+        <v>447430</v>
       </c>
       <c r="R29" t="n">
-        <v>6804619</v>
+        <v>6804548</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,10 +3458,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129893928</v>
+        <v>129893903</v>
       </c>
       <c r="B30" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3459,42 +3469,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447584</v>
+        <v>447486</v>
       </c>
       <c r="R30" t="n">
-        <v>6804698</v>
+        <v>6804619</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,41 +3555,40 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129893957</v>
+        <v>129893928</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3597,10 +3598,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447418</v>
+        <v>447584</v>
       </c>
       <c r="R31" t="n">
-        <v>6804561</v>
+        <v>6804698</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3641,7 +3642,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894005</v>
+        <v>129894001</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4289,19 +4289,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447574</v>
+        <v>447491</v>
       </c>
       <c r="R38" t="n">
-        <v>6804491</v>
+        <v>6804629</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4336,18 +4333,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4366,41 +4357,40 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129893962</v>
+        <v>129893927</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4410,10 +4400,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447552</v>
+        <v>447561</v>
       </c>
       <c r="R39" t="n">
-        <v>6804720</v>
+        <v>6804628</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4454,7 +4444,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4473,7 +4462,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894001</v>
+        <v>129894005</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4502,16 +4491,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447491</v>
+        <v>447574</v>
       </c>
       <c r="R40" t="n">
-        <v>6804629</v>
+        <v>6804491</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4546,12 +4538,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4570,40 +4568,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893927</v>
+        <v>129893962</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4613,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447561</v>
+        <v>447552</v>
       </c>
       <c r="R41" t="n">
-        <v>6804628</v>
+        <v>6804720</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4657,6 +4656,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4782,7 +4782,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894020</v>
+        <v>129894000</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -4817,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447306</v>
+        <v>447442</v>
       </c>
       <c r="R43" t="n">
-        <v>6804757</v>
+        <v>6804551</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,6 +4853,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,10 +4884,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894007</v>
+        <v>129893966</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4890,21 +4895,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4914,10 +4919,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447533</v>
+        <v>447483</v>
       </c>
       <c r="R44" t="n">
-        <v>6804620</v>
+        <v>6804616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4950,11 +4955,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4981,7 +4981,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894000</v>
+        <v>129893998</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447442</v>
+        <v>447424</v>
       </c>
       <c r="R45" t="n">
-        <v>6804551</v>
+        <v>6804554</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5052,11 +5052,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5083,10 +5078,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893966</v>
+        <v>129894020</v>
       </c>
       <c r="B46" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5094,21 +5089,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5118,10 +5113,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447483</v>
+        <v>447306</v>
       </c>
       <c r="R46" t="n">
-        <v>6804616</v>
+        <v>6804757</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5180,7 +5175,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893998</v>
+        <v>129894007</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5215,10 +5210,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447424</v>
+        <v>447533</v>
       </c>
       <c r="R47" t="n">
-        <v>6804554</v>
+        <v>6804620</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5251,6 +5246,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6467,6 +6467,3443 @@
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129893320</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>447517</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6804957</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129893335</v>
+      </c>
+      <c r="B61" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>447503</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6804998</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129893327</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80187</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>447580</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6804735</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129893319</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>447448</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6805081</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129893371</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>447415</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6804899</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129893373</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>447423</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6805054</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129893318</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>447384</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6805028</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129893369</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>447459</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6804815</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129893341</v>
+      </c>
+      <c r="B68" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>447580</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6804735</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129893317</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>447474</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6804817</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129893390</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>447328</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6804646</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129893337</v>
+      </c>
+      <c r="B71" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>447532</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6804904</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129893386</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>447304</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6804742</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129893380</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>447464</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6804730</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129893372</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>447411</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6804990</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129893387</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>447301</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6804727</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129893377</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>447573</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6804725</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129893336</v>
+      </c>
+      <c r="B77" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>447517</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6804963</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129893379</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>447553</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6804766</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 10 m</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129893292</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>447436</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6804760</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129893376</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>447576</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6804770</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129893340</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>447459</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6804731</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129893370</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>447480</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6804861</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129893375</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>447518</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6804907</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129893378</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>447564</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6804749</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129893293</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>447420</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6804795</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129893381</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>447451</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6804727</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129893382</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>447448</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6804705</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129893294</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>447422</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6805021</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129893338</v>
+      </c>
+      <c r="B89" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>447531</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6804885</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129893374</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>447470</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6805005</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129893321</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>447539</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6804888</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129893389</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>447326</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6804648</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129893388</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>447312</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6804705</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894015</v>
+        <v>129893911</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447460</v>
+        <v>447312</v>
       </c>
       <c r="R2" t="n">
-        <v>6804726</v>
+        <v>6804764</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129893911</v>
+        <v>129894015</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447312</v>
+        <v>447460</v>
       </c>
       <c r="R3" t="n">
-        <v>6804764</v>
+        <v>6804726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -3050,45 +3050,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893905</v>
+        <v>129893960</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447582</v>
+        <v>447591</v>
       </c>
       <c r="R26" t="n">
-        <v>6804515</v>
+        <v>6804697</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3129,6 +3138,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3147,54 +3157,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893960</v>
+        <v>129893905</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447591</v>
+        <v>447582</v>
       </c>
       <c r="R27" t="n">
-        <v>6804697</v>
+        <v>6804515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3235,7 +3236,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894001</v>
+        <v>129894005</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4289,16 +4289,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447491</v>
+        <v>447574</v>
       </c>
       <c r="R38" t="n">
-        <v>6804629</v>
+        <v>6804491</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4333,12 +4336,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4357,40 +4366,41 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129893927</v>
+        <v>129893962</v>
       </c>
       <c r="B39" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4400,10 +4410,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447561</v>
+        <v>447552</v>
       </c>
       <c r="R39" t="n">
-        <v>6804628</v>
+        <v>6804720</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4444,6 +4454,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4462,7 +4473,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894005</v>
+        <v>129894001</v>
       </c>
       <c r="B40" t="n">
         <v>79081</v>
@@ -4491,19 +4502,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447574</v>
+        <v>447491</v>
       </c>
       <c r="R40" t="n">
-        <v>6804491</v>
+        <v>6804629</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4538,18 +4546,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4568,41 +4570,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893962</v>
+        <v>129893927</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4612,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447552</v>
+        <v>447561</v>
       </c>
       <c r="R41" t="n">
-        <v>6804720</v>
+        <v>6804628</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4656,7 +4657,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4675,54 +4675,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129893959</v>
+        <v>129894020</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447540</v>
+        <v>447306</v>
       </c>
       <c r="R42" t="n">
-        <v>6804664</v>
+        <v>6804757</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4763,7 +4754,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4782,7 +4772,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894000</v>
+        <v>129894007</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -4817,10 +4807,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447442</v>
+        <v>447533</v>
       </c>
       <c r="R43" t="n">
-        <v>6804551</v>
+        <v>6804620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4857,7 +4847,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4884,45 +4874,54 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129893966</v>
+        <v>129893959</v>
       </c>
       <c r="B44" t="n">
-        <v>78838</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447483</v>
+        <v>447540</v>
       </c>
       <c r="R44" t="n">
-        <v>6804616</v>
+        <v>6804664</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4963,6 +4962,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4981,7 +4981,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893998</v>
+        <v>129894000</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447424</v>
+        <v>447442</v>
       </c>
       <c r="R45" t="n">
-        <v>6804554</v>
+        <v>6804551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5052,6 +5052,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5078,10 +5083,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894020</v>
+        <v>129893966</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5089,21 +5094,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5113,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447306</v>
+        <v>447483</v>
       </c>
       <c r="R46" t="n">
-        <v>6804757</v>
+        <v>6804616</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5175,7 +5180,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894007</v>
+        <v>129893998</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5210,10 +5215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447533</v>
+        <v>447424</v>
       </c>
       <c r="R47" t="n">
-        <v>6804620</v>
+        <v>6804554</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5246,11 +5251,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129893911</v>
+        <v>129894015</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447312</v>
+        <v>447460</v>
       </c>
       <c r="R2" t="n">
-        <v>6804764</v>
+        <v>6804726</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894015</v>
+        <v>129893911</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447460</v>
+        <v>447312</v>
       </c>
       <c r="R3" t="n">
-        <v>6804726</v>
+        <v>6804764</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893993</v>
+        <v>129894004</v>
       </c>
       <c r="B6" t="n">
         <v>79081</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447392</v>
+        <v>447553</v>
       </c>
       <c r="R6" t="n">
-        <v>6804569</v>
+        <v>6804480</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129894004</v>
+        <v>129893993</v>
       </c>
       <c r="B7" t="n">
         <v>79081</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447553</v>
+        <v>447392</v>
       </c>
       <c r="R7" t="n">
-        <v>6804480</v>
+        <v>6804569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129894014</v>
+        <v>129894008</v>
       </c>
       <c r="B8" t="n">
         <v>79081</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447482</v>
+        <v>447529</v>
       </c>
       <c r="R8" t="n">
-        <v>6804743</v>
+        <v>6804634</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129894008</v>
+        <v>129894014</v>
       </c>
       <c r="B9" t="n">
         <v>79081</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447529</v>
+        <v>447482</v>
       </c>
       <c r="R9" t="n">
-        <v>6804634</v>
+        <v>6804743</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129893941</v>
+        <v>129894022</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,31 +1564,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1596,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447578</v>
+        <v>447311</v>
       </c>
       <c r="R11" t="n">
-        <v>6804600</v>
+        <v>6804635</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1640,6 +1635,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1759,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894022</v>
+        <v>129893941</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1770,26 +1766,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1797,10 +1798,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447311</v>
+        <v>447578</v>
       </c>
       <c r="R13" t="n">
-        <v>6804635</v>
+        <v>6804600</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,7 +1842,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2256,53 +2256,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893922</v>
+        <v>129893904</v>
       </c>
       <c r="B18" t="n">
-        <v>56926</v>
+        <v>79700</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447455</v>
+        <v>447491</v>
       </c>
       <c r="R18" t="n">
-        <v>6804619</v>
+        <v>6804595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,45 +2353,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893904</v>
+        <v>129893922</v>
       </c>
       <c r="B19" t="n">
-        <v>79700</v>
+        <v>56926</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447491</v>
+        <v>447455</v>
       </c>
       <c r="R19" t="n">
-        <v>6804595</v>
+        <v>6804619</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894002</v>
+        <v>129893996</v>
       </c>
       <c r="B20" t="n">
         <v>79081</v>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447484</v>
+        <v>447398</v>
       </c>
       <c r="R20" t="n">
-        <v>6804623</v>
+        <v>6804577</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129893996</v>
+        <v>129894002</v>
       </c>
       <c r="B21" t="n">
         <v>79081</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447398</v>
+        <v>447484</v>
       </c>
       <c r="R21" t="n">
-        <v>6804577</v>
+        <v>6804623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894010</v>
+        <v>129893907</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,21 +2663,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447599</v>
+        <v>447541</v>
       </c>
       <c r="R22" t="n">
-        <v>6804708</v>
+        <v>6804663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2749,45 +2749,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894048</v>
+        <v>129893958</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447408</v>
+        <v>447566</v>
       </c>
       <c r="R23" t="n">
-        <v>6804651</v>
+        <v>6804650</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,6 +2837,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2846,10 +2856,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893907</v>
+        <v>129894048</v>
       </c>
       <c r="B24" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2857,21 +2867,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2881,10 +2891,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447541</v>
+        <v>447408</v>
       </c>
       <c r="R24" t="n">
-        <v>6804663</v>
+        <v>6804651</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2943,54 +2953,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129893958</v>
+        <v>129894010</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447566</v>
+        <v>447599</v>
       </c>
       <c r="R25" t="n">
-        <v>6804650</v>
+        <v>6804708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,7 +3032,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3050,54 +3050,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893960</v>
+        <v>129893905</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447591</v>
+        <v>447582</v>
       </c>
       <c r="R26" t="n">
-        <v>6804697</v>
+        <v>6804515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3138,7 +3129,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3157,45 +3147,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893905</v>
+        <v>129893960</v>
       </c>
       <c r="B27" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447582</v>
+        <v>447591</v>
       </c>
       <c r="R27" t="n">
-        <v>6804515</v>
+        <v>6804697</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3236,6 +3235,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3254,41 +3254,40 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893957</v>
+        <v>129893928</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3298,10 +3297,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447418</v>
+        <v>447584</v>
       </c>
       <c r="R28" t="n">
-        <v>6804561</v>
+        <v>6804698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3342,7 +3341,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3361,45 +3359,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893902</v>
+        <v>129893957</v>
       </c>
       <c r="B29" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447430</v>
+        <v>447418</v>
       </c>
       <c r="R29" t="n">
-        <v>6804548</v>
+        <v>6804561</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3440,6 +3447,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3458,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129893903</v>
+        <v>129894009</v>
       </c>
       <c r="B30" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3469,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3493,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447486</v>
+        <v>447538</v>
       </c>
       <c r="R30" t="n">
-        <v>6804619</v>
+        <v>6804692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3529,6 +3537,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3555,10 +3568,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129893928</v>
+        <v>129894011</v>
       </c>
       <c r="B31" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3566,42 +3579,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447584</v>
+        <v>447589</v>
       </c>
       <c r="R31" t="n">
-        <v>6804698</v>
+        <v>6804744</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3634,6 +3639,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3660,7 +3670,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894011</v>
+        <v>129894016</v>
       </c>
       <c r="B32" t="n">
         <v>79081</v>
@@ -3695,10 +3705,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447589</v>
+        <v>447444</v>
       </c>
       <c r="R32" t="n">
-        <v>6804744</v>
+        <v>6804723</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3731,11 +3741,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3762,10 +3767,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894009</v>
+        <v>129893903</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3773,21 +3778,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3797,10 +3802,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447538</v>
+        <v>447486</v>
       </c>
       <c r="R33" t="n">
-        <v>6804692</v>
+        <v>6804619</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3833,11 +3838,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3864,10 +3864,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894016</v>
+        <v>129893902</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3875,21 +3875,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447444</v>
+        <v>447430</v>
       </c>
       <c r="R34" t="n">
-        <v>6804723</v>
+        <v>6804548</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4058,10 +4058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129893916</v>
+        <v>129893929</v>
       </c>
       <c r="B36" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4069,34 +4069,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447402</v>
+        <v>447594</v>
       </c>
       <c r="R36" t="n">
-        <v>6804565</v>
+        <v>6804744</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4155,10 +4163,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129893929</v>
+        <v>129893916</v>
       </c>
       <c r="B37" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4166,42 +4174,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447594</v>
+        <v>447402</v>
       </c>
       <c r="R37" t="n">
-        <v>6804744</v>
+        <v>6804565</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894005</v>
+        <v>129894001</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4289,19 +4289,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447574</v>
+        <v>447491</v>
       </c>
       <c r="R38" t="n">
-        <v>6804491</v>
+        <v>6804629</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4336,18 +4333,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4366,43 +4357,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129893962</v>
+        <v>129894005</v>
       </c>
       <c r="B39" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4410,10 +4395,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447552</v>
+        <v>447574</v>
       </c>
       <c r="R39" t="n">
-        <v>6804720</v>
+        <v>6804491</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4446,6 +4431,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4473,10 +4463,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894001</v>
+        <v>129893927</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4484,34 +4474,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447491</v>
+        <v>447561</v>
       </c>
       <c r="R40" t="n">
-        <v>6804629</v>
+        <v>6804628</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4570,40 +4568,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893927</v>
+        <v>129893962</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4613,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447561</v>
+        <v>447552</v>
       </c>
       <c r="R41" t="n">
-        <v>6804628</v>
+        <v>6804720</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4657,6 +4656,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894020</v>
+        <v>129893998</v>
       </c>
       <c r="B42" t="n">
         <v>79081</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447306</v>
+        <v>447424</v>
       </c>
       <c r="R42" t="n">
-        <v>6804757</v>
+        <v>6804554</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4772,7 +4772,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894007</v>
+        <v>129894000</v>
       </c>
       <c r="B43" t="n">
         <v>79081</v>
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447533</v>
+        <v>447442</v>
       </c>
       <c r="R43" t="n">
-        <v>6804620</v>
+        <v>6804551</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4874,54 +4874,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129893959</v>
+        <v>129894020</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447540</v>
+        <v>447306</v>
       </c>
       <c r="R44" t="n">
-        <v>6804664</v>
+        <v>6804757</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4962,7 +4953,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4981,7 +4971,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894000</v>
+        <v>129894007</v>
       </c>
       <c r="B45" t="n">
         <v>79081</v>
@@ -5016,10 +5006,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447442</v>
+        <v>447533</v>
       </c>
       <c r="R45" t="n">
-        <v>6804551</v>
+        <v>6804620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5056,7 +5046,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5180,45 +5170,54 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893998</v>
+        <v>129893959</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447424</v>
+        <v>447540</v>
       </c>
       <c r="R47" t="n">
-        <v>6804554</v>
+        <v>6804664</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5259,6 +5258,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5374,10 +5374,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893931</v>
+        <v>129893906</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5385,42 +5385,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447545</v>
+        <v>447569</v>
       </c>
       <c r="R49" t="n">
-        <v>6804718</v>
+        <v>6804584</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5479,10 +5471,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893906</v>
+        <v>129893931</v>
       </c>
       <c r="B50" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5490,34 +5482,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447569</v>
+        <v>447545</v>
       </c>
       <c r="R50" t="n">
-        <v>6804584</v>
+        <v>6804718</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5576,7 +5576,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894006</v>
+        <v>129894021</v>
       </c>
       <c r="B51" t="n">
         <v>79081</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447575</v>
+        <v>447330</v>
       </c>
       <c r="R51" t="n">
-        <v>6804539</v>
+        <v>6804680</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,6 +5647,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5673,7 +5678,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894021</v>
+        <v>129894006</v>
       </c>
       <c r="B52" t="n">
         <v>79081</v>
@@ -5708,10 +5713,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447330</v>
+        <v>447575</v>
       </c>
       <c r="R52" t="n">
-        <v>6804680</v>
+        <v>6804539</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5744,11 +5749,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5979,10 +5979,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129893992</v>
+        <v>129893917</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447390</v>
+        <v>447580</v>
       </c>
       <c r="R55" t="n">
-        <v>6804568</v>
+        <v>6804527</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6050,11 +6050,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6081,10 +6076,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129893917</v>
+        <v>129893992</v>
       </c>
       <c r="B56" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6092,21 +6087,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6116,10 +6111,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447580</v>
+        <v>447390</v>
       </c>
       <c r="R56" t="n">
-        <v>6804527</v>
+        <v>6804568</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6152,6 +6147,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7087,10 +7087,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893318</v>
+        <v>129893369</v>
       </c>
       <c r="B66" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7098,42 +7098,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447384</v>
+        <v>447459</v>
       </c>
       <c r="R66" t="n">
-        <v>6805028</v>
+        <v>6804815</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7192,10 +7184,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893369</v>
+        <v>129893341</v>
       </c>
       <c r="B67" t="n">
-        <v>79081</v>
+        <v>80186</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7203,34 +7195,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447459</v>
+        <v>447580</v>
       </c>
       <c r="R67" t="n">
-        <v>6804815</v>
+        <v>6804735</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7265,12 +7260,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7289,10 +7290,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893341</v>
+        <v>129893318</v>
       </c>
       <c r="B68" t="n">
-        <v>80186</v>
+        <v>57733</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7300,26 +7301,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7327,10 +7333,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447580</v>
+        <v>447384</v>
       </c>
       <c r="R68" t="n">
-        <v>6804735</v>
+        <v>6805028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7365,18 +7371,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7500,45 +7500,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129893390</v>
+        <v>129893337</v>
       </c>
       <c r="B70" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447328</v>
+        <v>447532</v>
       </c>
       <c r="R70" t="n">
-        <v>6804646</v>
+        <v>6804904</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7579,6 +7588,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7597,54 +7607,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129893337</v>
+        <v>129893390</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447532</v>
+        <v>447328</v>
       </c>
       <c r="R71" t="n">
-        <v>6804904</v>
+        <v>6804646</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7685,7 +7686,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8005,7 +8005,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129893387</v>
+        <v>129893377</v>
       </c>
       <c r="B75" t="n">
         <v>79081</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447301</v>
+        <v>447573</v>
       </c>
       <c r="R75" t="n">
-        <v>6804727</v>
+        <v>6804725</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129893377</v>
+        <v>129893387</v>
       </c>
       <c r="B76" t="n">
         <v>79081</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447573</v>
+        <v>447301</v>
       </c>
       <c r="R76" t="n">
-        <v>6804725</v>
+        <v>6804727</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8199,54 +8199,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129893336</v>
+        <v>129893379</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447517</v>
+        <v>447553</v>
       </c>
       <c r="R77" t="n">
-        <v>6804963</v>
+        <v>6804766</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8281,13 +8272,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 10 m</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8306,45 +8301,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893379</v>
+        <v>129893336</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447553</v>
+        <v>447517</v>
       </c>
       <c r="R78" t="n">
-        <v>6804766</v>
+        <v>6804963</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8379,17 +8383,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 10 m</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9010,10 +9010,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893293</v>
+        <v>129893381</v>
       </c>
       <c r="B85" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9021,21 +9021,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447420</v>
+        <v>447451</v>
       </c>
       <c r="R85" t="n">
-        <v>6804795</v>
+        <v>6804727</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9107,10 +9107,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893381</v>
+        <v>129893293</v>
       </c>
       <c r="B86" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9118,21 +9118,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9142,10 +9142,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447451</v>
+        <v>447420</v>
       </c>
       <c r="R86" t="n">
-        <v>6804727</v>
+        <v>6804795</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9204,45 +9204,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129893382</v>
+        <v>129893338</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447448</v>
+        <v>447531</v>
       </c>
       <c r="R87" t="n">
-        <v>6804705</v>
+        <v>6804885</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9283,6 +9292,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9301,10 +9311,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893294</v>
+        <v>129893382</v>
       </c>
       <c r="B88" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9312,21 +9322,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9336,10 +9346,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447422</v>
+        <v>447448</v>
       </c>
       <c r="R88" t="n">
-        <v>6805021</v>
+        <v>6804705</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9398,54 +9408,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893338</v>
+        <v>129893294</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79700</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447531</v>
+        <v>447422</v>
       </c>
       <c r="R89" t="n">
-        <v>6804885</v>
+        <v>6805021</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9486,7 +9487,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9505,7 +9505,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893374</v>
+        <v>129893388</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447470</v>
+        <v>447312</v>
       </c>
       <c r="R90" t="n">
-        <v>6805005</v>
+        <v>6804705</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9576,11 +9576,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9607,10 +9602,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893321</v>
+        <v>129893374</v>
       </c>
       <c r="B91" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9618,42 +9613,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447539</v>
+        <v>447470</v>
       </c>
       <c r="R91" t="n">
-        <v>6804888</v>
+        <v>6805005</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9686,6 +9673,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9809,10 +9801,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893388</v>
+        <v>129893321</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9820,34 +9812,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447312</v>
+        <v>447539</v>
       </c>
       <c r="R93" t="n">
-        <v>6804705</v>
+        <v>6804888</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -2749,54 +2749,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129893958</v>
+        <v>129894048</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447566</v>
+        <v>447408</v>
       </c>
       <c r="R23" t="n">
-        <v>6804650</v>
+        <v>6804651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2837,7 +2828,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2856,7 +2846,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894048</v>
+        <v>129894010</v>
       </c>
       <c r="B24" t="n">
         <v>79081</v>
@@ -2891,10 +2881,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447408</v>
+        <v>447599</v>
       </c>
       <c r="R24" t="n">
-        <v>6804651</v>
+        <v>6804708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2953,45 +2943,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129894010</v>
+        <v>129893958</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447599</v>
+        <v>447566</v>
       </c>
       <c r="R25" t="n">
-        <v>6804708</v>
+        <v>6804650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3032,6 +3031,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -4463,40 +4463,41 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129893927</v>
+        <v>129893962</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4506,10 +4507,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447561</v>
+        <v>447552</v>
       </c>
       <c r="R40" t="n">
-        <v>6804628</v>
+        <v>6804720</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4550,6 +4551,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4568,41 +4570,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893962</v>
+        <v>129893927</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4612,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447552</v>
+        <v>447561</v>
       </c>
       <c r="R41" t="n">
-        <v>6804720</v>
+        <v>6804628</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4656,7 +4657,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -9204,54 +9204,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129893338</v>
+        <v>129893382</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447531</v>
+        <v>447448</v>
       </c>
       <c r="R87" t="n">
-        <v>6804885</v>
+        <v>6804705</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9292,7 +9283,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9311,10 +9301,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893382</v>
+        <v>129893294</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9322,21 +9312,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9346,10 +9336,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447448</v>
+        <v>447422</v>
       </c>
       <c r="R88" t="n">
-        <v>6804705</v>
+        <v>6805021</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9408,45 +9398,54 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893294</v>
+        <v>129893338</v>
       </c>
       <c r="B89" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447422</v>
+        <v>447531</v>
       </c>
       <c r="R89" t="n">
-        <v>6805021</v>
+        <v>6804885</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9487,6 +9486,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9505,10 +9505,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893388</v>
+        <v>129893321</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9516,34 +9516,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447312</v>
+        <v>447539</v>
       </c>
       <c r="R90" t="n">
-        <v>6804705</v>
+        <v>6804888</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9602,7 +9610,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893374</v>
+        <v>129893388</v>
       </c>
       <c r="B91" t="n">
         <v>79081</v>
@@ -9637,10 +9645,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447470</v>
+        <v>447312</v>
       </c>
       <c r="R91" t="n">
-        <v>6805005</v>
+        <v>6804705</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9673,11 +9681,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9704,7 +9707,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893389</v>
+        <v>129893374</v>
       </c>
       <c r="B92" t="n">
         <v>79081</v>
@@ -9739,10 +9742,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447326</v>
+        <v>447470</v>
       </c>
       <c r="R92" t="n">
-        <v>6804648</v>
+        <v>6805005</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9775,6 +9778,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9801,10 +9809,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893321</v>
+        <v>129893389</v>
       </c>
       <c r="B93" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9812,42 +9820,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447539</v>
+        <v>447326</v>
       </c>
       <c r="R93" t="n">
-        <v>6804888</v>
+        <v>6804648</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129894015</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129893911</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893947</v>
+        <v>129893997</v>
       </c>
       <c r="B4" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447580</v>
+        <v>447419</v>
       </c>
       <c r="R4" t="n">
-        <v>6804504</v>
+        <v>6804565</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893997</v>
+        <v>129893947</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447419</v>
+        <v>447580</v>
       </c>
       <c r="R5" t="n">
-        <v>6804565</v>
+        <v>6804504</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129894004</v>
+        <v>129893993</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447553</v>
+        <v>447392</v>
       </c>
       <c r="R6" t="n">
-        <v>6804480</v>
+        <v>6804569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893993</v>
+        <v>129894004</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447392</v>
+        <v>447553</v>
       </c>
       <c r="R7" t="n">
-        <v>6804569</v>
+        <v>6804480</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
         <v>129894008</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129894014</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129893994</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129894022</v>
+        <v>129893941</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,26 +1564,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1591,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447311</v>
+        <v>447578</v>
       </c>
       <c r="R11" t="n">
-        <v>6804635</v>
+        <v>6804600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1635,7 +1640,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1657,7 +1661,7 @@
         <v>129894003</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,10 +1759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129893941</v>
+        <v>129894022</v>
       </c>
       <c r="B13" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,31 +1770,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1798,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447578</v>
+        <v>447311</v>
       </c>
       <c r="R13" t="n">
-        <v>6804600</v>
+        <v>6804635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,6 +1841,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893915</v>
+        <v>129893930</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,34 +1871,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447563</v>
+        <v>447566</v>
       </c>
       <c r="R14" t="n">
-        <v>6804478</v>
+        <v>6804736</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,10 +1965,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893901</v>
+        <v>129893915</v>
       </c>
       <c r="B15" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1992,10 +2000,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447394</v>
+        <v>447563</v>
       </c>
       <c r="R15" t="n">
-        <v>6804571</v>
+        <v>6804478</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,10 +2062,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129893909</v>
+        <v>129893901</v>
       </c>
       <c r="B16" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447445</v>
+        <v>447394</v>
       </c>
       <c r="R16" t="n">
-        <v>6804759</v>
+        <v>6804571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,10 +2159,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893930</v>
+        <v>129893909</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,42 +2170,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447566</v>
+        <v>447445</v>
       </c>
       <c r="R17" t="n">
-        <v>6804736</v>
+        <v>6804759</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,45 +2256,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893904</v>
+        <v>129893922</v>
       </c>
       <c r="B18" t="n">
-        <v>79700</v>
+        <v>56927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447491</v>
+        <v>447455</v>
       </c>
       <c r="R18" t="n">
-        <v>6804595</v>
+        <v>6804619</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,53 +2361,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893922</v>
+        <v>129893904</v>
       </c>
       <c r="B19" t="n">
-        <v>56926</v>
+        <v>79703</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447455</v>
+        <v>447491</v>
       </c>
       <c r="R19" t="n">
-        <v>6804619</v>
+        <v>6804595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893996</v>
+        <v>129894002</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447398</v>
+        <v>447484</v>
       </c>
       <c r="R20" t="n">
-        <v>6804577</v>
+        <v>6804623</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894002</v>
+        <v>129893996</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447484</v>
+        <v>447398</v>
       </c>
       <c r="R21" t="n">
-        <v>6804623</v>
+        <v>6804577</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129893907</v>
+        <v>129894048</v>
       </c>
       <c r="B22" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,21 +2663,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447541</v>
+        <v>447408</v>
       </c>
       <c r="R22" t="n">
-        <v>6804663</v>
+        <v>6804651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2749,10 +2749,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894048</v>
+        <v>129894010</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447408</v>
+        <v>447599</v>
       </c>
       <c r="R23" t="n">
-        <v>6804651</v>
+        <v>6804708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894010</v>
+        <v>129893907</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2857,21 +2857,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447599</v>
+        <v>447541</v>
       </c>
       <c r="R24" t="n">
-        <v>6804708</v>
+        <v>6804663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3053,7 +3053,7 @@
         <v>129893905</v>
       </c>
       <c r="B26" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893928</v>
+        <v>129894016</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3265,42 +3265,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447584</v>
+        <v>447444</v>
       </c>
       <c r="R28" t="n">
-        <v>6804698</v>
+        <v>6804723</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3359,54 +3351,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893957</v>
+        <v>129894009</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447418</v>
+        <v>447538</v>
       </c>
       <c r="R29" t="n">
-        <v>6804561</v>
+        <v>6804692</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3441,13 +3424,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3466,10 +3453,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894009</v>
+        <v>129894011</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3501,10 +3488,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447538</v>
+        <v>447589</v>
       </c>
       <c r="R30" t="n">
-        <v>6804692</v>
+        <v>6804744</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3541,7 +3528,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3568,10 +3555,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894011</v>
+        <v>129893903</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3579,21 +3566,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3603,10 +3590,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447589</v>
+        <v>447486</v>
       </c>
       <c r="R31" t="n">
-        <v>6804744</v>
+        <v>6804619</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3639,11 +3626,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3670,10 +3652,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894016</v>
+        <v>129893902</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3681,21 +3663,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3705,10 +3687,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447444</v>
+        <v>447430</v>
       </c>
       <c r="R32" t="n">
-        <v>6804723</v>
+        <v>6804548</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3767,10 +3749,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893903</v>
+        <v>129893928</v>
       </c>
       <c r="B33" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3778,34 +3760,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447486</v>
+        <v>447584</v>
       </c>
       <c r="R33" t="n">
-        <v>6804619</v>
+        <v>6804698</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3864,45 +3854,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893902</v>
+        <v>129893957</v>
       </c>
       <c r="B34" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447430</v>
+        <v>447418</v>
       </c>
       <c r="R34" t="n">
-        <v>6804548</v>
+        <v>6804561</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3943,6 +3942,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129893908</v>
+        <v>129893929</v>
       </c>
       <c r="B35" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3972,34 +3972,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447543</v>
+        <v>447594</v>
       </c>
       <c r="R35" t="n">
-        <v>6804684</v>
+        <v>6804744</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4058,10 +4066,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129893929</v>
+        <v>129893908</v>
       </c>
       <c r="B36" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4069,42 +4077,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447594</v>
+        <v>447543</v>
       </c>
       <c r="R36" t="n">
-        <v>6804744</v>
+        <v>6804684</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4166,7 +4166,7 @@
         <v>129893916</v>
       </c>
       <c r="B37" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894001</v>
+        <v>129894005</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4289,16 +4289,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447491</v>
+        <v>447574</v>
       </c>
       <c r="R38" t="n">
-        <v>6804629</v>
+        <v>6804491</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4333,12 +4336,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4357,10 +4366,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894005</v>
+        <v>129894001</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4386,19 +4395,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447574</v>
+        <v>447491</v>
       </c>
       <c r="R39" t="n">
-        <v>6804491</v>
+        <v>6804629</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4433,18 +4439,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4463,41 +4463,40 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129893962</v>
+        <v>129893927</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4507,10 +4506,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447552</v>
+        <v>447561</v>
       </c>
       <c r="R40" t="n">
-        <v>6804720</v>
+        <v>6804628</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4550,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4570,40 +4568,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893927</v>
+        <v>129893962</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4613,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447561</v>
+        <v>447552</v>
       </c>
       <c r="R41" t="n">
-        <v>6804628</v>
+        <v>6804720</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4657,6 +4656,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>129893998</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894000</v>
+        <v>129894007</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4807,10 +4807,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447442</v>
+        <v>447533</v>
       </c>
       <c r="R43" t="n">
-        <v>6804551</v>
+        <v>6804620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4874,10 +4874,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894020</v>
+        <v>129894000</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447306</v>
+        <v>447442</v>
       </c>
       <c r="R44" t="n">
-        <v>6804757</v>
+        <v>6804551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4945,6 +4945,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4971,10 +4976,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894007</v>
+        <v>129894020</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5006,10 +5011,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447533</v>
+        <v>447306</v>
       </c>
       <c r="R45" t="n">
-        <v>6804620</v>
+        <v>6804757</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5042,11 +5047,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5076,7 +5076,7 @@
         <v>129893966</v>
       </c>
       <c r="B46" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>129893999</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5374,10 +5374,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893906</v>
+        <v>129893931</v>
       </c>
       <c r="B49" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5385,34 +5385,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447569</v>
+        <v>447545</v>
       </c>
       <c r="R49" t="n">
-        <v>6804584</v>
+        <v>6804718</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5471,10 +5479,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893931</v>
+        <v>129893906</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5482,42 +5490,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447545</v>
+        <v>447569</v>
       </c>
       <c r="R50" t="n">
-        <v>6804718</v>
+        <v>6804584</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5579,7 +5579,7 @@
         <v>129894021</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>129894006</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>129893995</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129893917</v>
+        <v>129893992</v>
       </c>
       <c r="B55" t="n">
-        <v>79671</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447580</v>
+        <v>447390</v>
       </c>
       <c r="R55" t="n">
-        <v>6804527</v>
+        <v>6804568</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6050,6 +6050,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6076,10 +6081,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129893992</v>
+        <v>129893917</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>79674</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6087,21 +6092,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6111,10 +6116,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447390</v>
+        <v>447580</v>
       </c>
       <c r="R56" t="n">
-        <v>6804568</v>
+        <v>6804527</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6147,11 +6152,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6178,10 +6178,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129894013</v>
+        <v>129893910</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6189,21 +6189,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447519</v>
+        <v>447424</v>
       </c>
       <c r="R57" t="n">
-        <v>6804713</v>
+        <v>6804723</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6278,7 +6278,7 @@
         <v>129894012</v>
       </c>
       <c r="B58" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893910</v>
+        <v>129894013</v>
       </c>
       <c r="B59" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447424</v>
+        <v>447519</v>
       </c>
       <c r="R59" t="n">
-        <v>6804723</v>
+        <v>6804713</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6469,40 +6469,41 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893320</v>
+        <v>129893335</v>
       </c>
       <c r="B60" t="n">
-        <v>57733</v>
+        <v>8450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6512,10 +6513,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447517</v>
+        <v>447503</v>
       </c>
       <c r="R60" t="n">
-        <v>6804957</v>
+        <v>6804998</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,6 +6557,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6574,41 +6576,40 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893335</v>
+        <v>129893320</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6618,10 +6619,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447503</v>
+        <v>447517</v>
       </c>
       <c r="R61" t="n">
-        <v>6804998</v>
+        <v>6804957</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6663,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>129893327</v>
       </c>
       <c r="B62" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>129893319</v>
       </c>
       <c r="B63" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>129893371</v>
       </c>
       <c r="B64" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>129893373</v>
       </c>
       <c r="B65" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7087,10 +7087,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893369</v>
+        <v>129893318</v>
       </c>
       <c r="B66" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7098,34 +7098,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447459</v>
+        <v>447384</v>
       </c>
       <c r="R66" t="n">
-        <v>6804815</v>
+        <v>6805028</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7187,7 +7195,7 @@
         <v>129893341</v>
       </c>
       <c r="B67" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7290,10 +7298,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893318</v>
+        <v>129893369</v>
       </c>
       <c r="B68" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7301,42 +7309,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447384</v>
+        <v>447459</v>
       </c>
       <c r="R68" t="n">
-        <v>6805028</v>
+        <v>6804815</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7398,7 +7398,7 @@
         <v>129893317</v>
       </c>
       <c r="B69" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7500,54 +7500,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129893337</v>
+        <v>129893390</v>
       </c>
       <c r="B70" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447532</v>
+        <v>447328</v>
       </c>
       <c r="R70" t="n">
-        <v>6804904</v>
+        <v>6804646</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7588,7 +7579,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7607,45 +7597,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129893390</v>
+        <v>129893337</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447328</v>
+        <v>447532</v>
       </c>
       <c r="R71" t="n">
-        <v>6804646</v>
+        <v>6804904</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7686,6 +7685,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7704,10 +7704,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129893386</v>
+        <v>129893380</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447304</v>
+        <v>447464</v>
       </c>
       <c r="R72" t="n">
-        <v>6804742</v>
+        <v>6804730</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7775,6 +7775,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7801,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129893380</v>
+        <v>129893386</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7836,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447464</v>
+        <v>447304</v>
       </c>
       <c r="R73" t="n">
-        <v>6804730</v>
+        <v>6804742</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7872,11 +7877,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7906,7 +7906,7 @@
         <v>129893372</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8005,10 +8005,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129893377</v>
+        <v>129893387</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447573</v>
+        <v>447301</v>
       </c>
       <c r="R75" t="n">
-        <v>6804725</v>
+        <v>6804727</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8102,10 +8102,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129893387</v>
+        <v>129893377</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447301</v>
+        <v>447573</v>
       </c>
       <c r="R76" t="n">
-        <v>6804727</v>
+        <v>6804725</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8202,7 +8202,7 @@
         <v>129893379</v>
       </c>
       <c r="B77" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>129893292</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>129893376</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>129893370</v>
       </c>
       <c r="B82" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>129893375</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>129893378</v>
       </c>
       <c r="B84" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>129893381</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>129893293</v>
       </c>
       <c r="B86" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>129893382</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9301,45 +9301,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893294</v>
+        <v>129893338</v>
       </c>
       <c r="B88" t="n">
-        <v>79700</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447422</v>
+        <v>447531</v>
       </c>
       <c r="R88" t="n">
-        <v>6805021</v>
+        <v>6804885</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9380,6 +9389,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9398,54 +9408,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893338</v>
+        <v>129893294</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447531</v>
+        <v>447422</v>
       </c>
       <c r="R89" t="n">
-        <v>6804885</v>
+        <v>6805021</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9486,7 +9487,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9508,7 +9508,7 @@
         <v>129893321</v>
       </c>
       <c r="B90" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9610,10 +9610,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893388</v>
+        <v>129893374</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9645,10 +9645,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447312</v>
+        <v>447470</v>
       </c>
       <c r="R91" t="n">
-        <v>6804705</v>
+        <v>6805005</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9681,6 +9681,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9707,10 +9712,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893374</v>
+        <v>129893389</v>
       </c>
       <c r="B92" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9742,10 +9747,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447470</v>
+        <v>447326</v>
       </c>
       <c r="R92" t="n">
-        <v>6805005</v>
+        <v>6804648</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9778,11 +9783,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9809,10 +9809,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893389</v>
+        <v>129893388</v>
       </c>
       <c r="B93" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9844,10 +9844,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447326</v>
+        <v>447312</v>
       </c>
       <c r="R93" t="n">
-        <v>6804648</v>
+        <v>6804705</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894015</v>
+        <v>129893911</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447460</v>
+        <v>447312</v>
       </c>
       <c r="R2" t="n">
-        <v>6804726</v>
+        <v>6804764</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129893911</v>
+        <v>129894015</v>
       </c>
       <c r="B3" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447312</v>
+        <v>447460</v>
       </c>
       <c r="R3" t="n">
-        <v>6804764</v>
+        <v>6804726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893997</v>
+        <v>129893947</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447419</v>
+        <v>447580</v>
       </c>
       <c r="R4" t="n">
-        <v>6804565</v>
+        <v>6804504</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893947</v>
+        <v>129893997</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447580</v>
+        <v>447419</v>
       </c>
       <c r="R5" t="n">
-        <v>6804504</v>
+        <v>6804565</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129893941</v>
+        <v>129894003</v>
       </c>
       <c r="B11" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,31 +1564,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1596,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447578</v>
+        <v>447489</v>
       </c>
       <c r="R11" t="n">
-        <v>6804600</v>
+        <v>6804602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1640,6 +1635,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1658,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894003</v>
+        <v>129894022</v>
       </c>
       <c r="B12" t="n">
         <v>79084</v>
@@ -1696,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447489</v>
+        <v>447311</v>
       </c>
       <c r="R12" t="n">
-        <v>6804602</v>
+        <v>6804635</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1759,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894022</v>
+        <v>129893941</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1770,26 +1766,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1797,10 +1798,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447311</v>
+        <v>447578</v>
       </c>
       <c r="R13" t="n">
-        <v>6804635</v>
+        <v>6804600</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,7 +1842,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893930</v>
+        <v>129893915</v>
       </c>
       <c r="B14" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,42 +1871,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447566</v>
+        <v>447563</v>
       </c>
       <c r="R14" t="n">
-        <v>6804736</v>
+        <v>6804478</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,7 +1957,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893915</v>
+        <v>129893901</v>
       </c>
       <c r="B15" t="n">
         <v>79703</v>
@@ -2000,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447563</v>
+        <v>447394</v>
       </c>
       <c r="R15" t="n">
-        <v>6804478</v>
+        <v>6804571</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,7 +2054,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129893901</v>
+        <v>129893909</v>
       </c>
       <c r="B16" t="n">
         <v>79703</v>
@@ -2097,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447394</v>
+        <v>447445</v>
       </c>
       <c r="R16" t="n">
-        <v>6804571</v>
+        <v>6804759</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2159,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893909</v>
+        <v>129893930</v>
       </c>
       <c r="B17" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,34 +2162,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447445</v>
+        <v>447566</v>
       </c>
       <c r="R17" t="n">
-        <v>6804759</v>
+        <v>6804736</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,53 +2256,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893922</v>
+        <v>129893904</v>
       </c>
       <c r="B18" t="n">
-        <v>56927</v>
+        <v>79703</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447455</v>
+        <v>447491</v>
       </c>
       <c r="R18" t="n">
-        <v>6804619</v>
+        <v>6804595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,45 +2353,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893904</v>
+        <v>129893922</v>
       </c>
       <c r="B19" t="n">
-        <v>79703</v>
+        <v>56927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447491</v>
+        <v>447455</v>
       </c>
       <c r="R19" t="n">
-        <v>6804595</v>
+        <v>6804619</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894002</v>
+        <v>129893996</v>
       </c>
       <c r="B20" t="n">
         <v>79084</v>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447484</v>
+        <v>447398</v>
       </c>
       <c r="R20" t="n">
-        <v>6804623</v>
+        <v>6804577</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129893996</v>
+        <v>129894002</v>
       </c>
       <c r="B21" t="n">
         <v>79084</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447398</v>
+        <v>447484</v>
       </c>
       <c r="R21" t="n">
-        <v>6804577</v>
+        <v>6804623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894048</v>
+        <v>129893907</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,21 +2663,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447408</v>
+        <v>447541</v>
       </c>
       <c r="R22" t="n">
-        <v>6804651</v>
+        <v>6804663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2749,7 +2749,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894010</v>
+        <v>129894048</v>
       </c>
       <c r="B23" t="n">
         <v>79084</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447599</v>
+        <v>447408</v>
       </c>
       <c r="R23" t="n">
-        <v>6804708</v>
+        <v>6804651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893907</v>
+        <v>129894010</v>
       </c>
       <c r="B24" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2857,21 +2857,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447541</v>
+        <v>447599</v>
       </c>
       <c r="R24" t="n">
-        <v>6804663</v>
+        <v>6804708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,45 +3050,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893905</v>
+        <v>129893960</v>
       </c>
       <c r="B26" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447582</v>
+        <v>447591</v>
       </c>
       <c r="R26" t="n">
-        <v>6804515</v>
+        <v>6804697</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3129,6 +3138,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3147,54 +3157,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893960</v>
+        <v>129893905</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447591</v>
+        <v>447582</v>
       </c>
       <c r="R27" t="n">
-        <v>6804697</v>
+        <v>6804515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3235,7 +3236,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129893929</v>
+        <v>129893908</v>
       </c>
       <c r="B35" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3972,42 +3972,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447594</v>
+        <v>447543</v>
       </c>
       <c r="R35" t="n">
-        <v>6804744</v>
+        <v>6804684</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,10 +4058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129893908</v>
+        <v>129893929</v>
       </c>
       <c r="B36" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4077,34 +4069,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447543</v>
+        <v>447594</v>
       </c>
       <c r="R36" t="n">
-        <v>6804684</v>
+        <v>6804744</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4463,40 +4463,41 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129893927</v>
+        <v>129893962</v>
       </c>
       <c r="B40" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -4506,10 +4507,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447561</v>
+        <v>447552</v>
       </c>
       <c r="R40" t="n">
-        <v>6804628</v>
+        <v>6804720</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4550,6 +4551,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4568,41 +4570,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893962</v>
+        <v>129893927</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4612,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447552</v>
+        <v>447561</v>
       </c>
       <c r="R41" t="n">
-        <v>6804720</v>
+        <v>6804628</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4656,7 +4657,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129893998</v>
+        <v>129894000</v>
       </c>
       <c r="B42" t="n">
         <v>79084</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447424</v>
+        <v>447442</v>
       </c>
       <c r="R42" t="n">
-        <v>6804554</v>
+        <v>6804551</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4746,6 +4746,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4772,7 +4777,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894007</v>
+        <v>129894020</v>
       </c>
       <c r="B43" t="n">
         <v>79084</v>
@@ -4807,10 +4812,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447533</v>
+        <v>447306</v>
       </c>
       <c r="R43" t="n">
-        <v>6804620</v>
+        <v>6804757</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4843,11 +4848,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4874,10 +4874,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894000</v>
+        <v>129893966</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,21 +4885,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447442</v>
+        <v>447483</v>
       </c>
       <c r="R44" t="n">
-        <v>6804551</v>
+        <v>6804616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4945,11 +4945,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4976,7 +4971,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894020</v>
+        <v>129893998</v>
       </c>
       <c r="B45" t="n">
         <v>79084</v>
@@ -5011,10 +5006,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447306</v>
+        <v>447424</v>
       </c>
       <c r="R45" t="n">
-        <v>6804757</v>
+        <v>6804554</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5073,10 +5068,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893966</v>
+        <v>129894007</v>
       </c>
       <c r="B46" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5084,21 +5079,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5108,10 +5103,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447483</v>
+        <v>447533</v>
       </c>
       <c r="R46" t="n">
-        <v>6804616</v>
+        <v>6804620</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5144,6 +5139,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5979,10 +5979,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129893992</v>
+        <v>129893917</v>
       </c>
       <c r="B55" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447390</v>
+        <v>447580</v>
       </c>
       <c r="R55" t="n">
-        <v>6804568</v>
+        <v>6804527</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6050,11 +6050,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6081,10 +6076,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129893917</v>
+        <v>129893992</v>
       </c>
       <c r="B56" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6092,21 +6087,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6116,10 +6111,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447580</v>
+        <v>447390</v>
       </c>
       <c r="R56" t="n">
-        <v>6804527</v>
+        <v>6804568</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6152,6 +6147,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6178,10 +6178,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129893910</v>
+        <v>129894013</v>
       </c>
       <c r="B57" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6189,21 +6189,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447424</v>
+        <v>447519</v>
       </c>
       <c r="R57" t="n">
-        <v>6804723</v>
+        <v>6804713</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129894013</v>
+        <v>129893910</v>
       </c>
       <c r="B59" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447519</v>
+        <v>447424</v>
       </c>
       <c r="R59" t="n">
-        <v>6804713</v>
+        <v>6804723</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6469,41 +6469,40 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893335</v>
+        <v>129893320</v>
       </c>
       <c r="B60" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6513,10 +6512,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447503</v>
+        <v>447517</v>
       </c>
       <c r="R60" t="n">
-        <v>6804998</v>
+        <v>6804957</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6557,7 +6556,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6576,40 +6574,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893320</v>
+        <v>129893335</v>
       </c>
       <c r="B61" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6619,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447517</v>
+        <v>447503</v>
       </c>
       <c r="R61" t="n">
-        <v>6804957</v>
+        <v>6804998</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6663,6 +6662,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7087,10 +7087,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893318</v>
+        <v>129893341</v>
       </c>
       <c r="B66" t="n">
-        <v>57734</v>
+        <v>80189</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7098,31 +7098,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7130,10 +7125,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447384</v>
+        <v>447580</v>
       </c>
       <c r="R66" t="n">
-        <v>6805028</v>
+        <v>6804735</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7168,12 +7163,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7192,10 +7193,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893341</v>
+        <v>129893318</v>
       </c>
       <c r="B67" t="n">
-        <v>80189</v>
+        <v>57734</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7203,26 +7204,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7230,10 +7236,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447580</v>
+        <v>447384</v>
       </c>
       <c r="R67" t="n">
-        <v>6804735</v>
+        <v>6805028</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7268,18 +7274,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8199,45 +8199,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129893379</v>
+        <v>129893336</v>
       </c>
       <c r="B77" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447553</v>
+        <v>447517</v>
       </c>
       <c r="R77" t="n">
-        <v>6804766</v>
+        <v>6804963</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8272,17 +8281,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 10 m</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8301,54 +8306,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893336</v>
+        <v>129893379</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447517</v>
+        <v>447553</v>
       </c>
       <c r="R78" t="n">
-        <v>6804963</v>
+        <v>6804766</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8383,13 +8379,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 10 m</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9010,10 +9010,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893381</v>
+        <v>129893293</v>
       </c>
       <c r="B85" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9021,21 +9021,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447451</v>
+        <v>447420</v>
       </c>
       <c r="R85" t="n">
-        <v>6804727</v>
+        <v>6804795</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9107,10 +9107,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893293</v>
+        <v>129893381</v>
       </c>
       <c r="B86" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9118,21 +9118,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9142,10 +9142,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447420</v>
+        <v>447451</v>
       </c>
       <c r="R86" t="n">
-        <v>6804795</v>
+        <v>6804727</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9204,10 +9204,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129893382</v>
+        <v>129893294</v>
       </c>
       <c r="B87" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9215,21 +9215,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447448</v>
+        <v>447422</v>
       </c>
       <c r="R87" t="n">
-        <v>6804705</v>
+        <v>6805021</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9408,10 +9408,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893294</v>
+        <v>129893382</v>
       </c>
       <c r="B89" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9419,21 +9419,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447422</v>
+        <v>447448</v>
       </c>
       <c r="R89" t="n">
-        <v>6805021</v>
+        <v>6804705</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129893911</v>
+        <v>129894015</v>
       </c>
       <c r="B2" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447312</v>
+        <v>447460</v>
       </c>
       <c r="R2" t="n">
-        <v>6804764</v>
+        <v>6804726</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894015</v>
+        <v>129893911</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447460</v>
+        <v>447312</v>
       </c>
       <c r="R3" t="n">
-        <v>6804726</v>
+        <v>6804764</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893947</v>
+        <v>129893997</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447580</v>
+        <v>447419</v>
       </c>
       <c r="R4" t="n">
-        <v>6804504</v>
+        <v>6804565</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893997</v>
+        <v>129893947</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447419</v>
+        <v>447580</v>
       </c>
       <c r="R5" t="n">
-        <v>6804565</v>
+        <v>6804504</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893996</v>
+        <v>129894002</v>
       </c>
       <c r="B20" t="n">
         <v>79084</v>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447398</v>
+        <v>447484</v>
       </c>
       <c r="R20" t="n">
-        <v>6804577</v>
+        <v>6804623</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894002</v>
+        <v>129893996</v>
       </c>
       <c r="B21" t="n">
         <v>79084</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447484</v>
+        <v>447398</v>
       </c>
       <c r="R21" t="n">
-        <v>6804623</v>
+        <v>6804577</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3050,54 +3050,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893960</v>
+        <v>129893905</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>79703</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447591</v>
+        <v>447582</v>
       </c>
       <c r="R26" t="n">
-        <v>6804697</v>
+        <v>6804515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3138,7 +3129,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3157,45 +3147,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893905</v>
+        <v>129893960</v>
       </c>
       <c r="B27" t="n">
-        <v>79703</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447582</v>
+        <v>447591</v>
       </c>
       <c r="R27" t="n">
-        <v>6804515</v>
+        <v>6804697</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3236,6 +3235,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894016</v>
+        <v>129893903</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3265,21 +3265,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447444</v>
+        <v>447486</v>
       </c>
       <c r="R28" t="n">
-        <v>6804723</v>
+        <v>6804619</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894009</v>
+        <v>129893902</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3362,21 +3362,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447538</v>
+        <v>447430</v>
       </c>
       <c r="R29" t="n">
-        <v>6804692</v>
+        <v>6804548</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3422,11 +3422,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3453,10 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894011</v>
+        <v>129893928</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3464,34 +3459,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447589</v>
+        <v>447584</v>
       </c>
       <c r="R30" t="n">
-        <v>6804744</v>
+        <v>6804698</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3524,11 +3527,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3555,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129893903</v>
+        <v>129894016</v>
       </c>
       <c r="B31" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3566,21 +3564,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3590,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447486</v>
+        <v>447444</v>
       </c>
       <c r="R31" t="n">
-        <v>6804619</v>
+        <v>6804723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3652,10 +3650,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129893902</v>
+        <v>129894009</v>
       </c>
       <c r="B32" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3663,21 +3661,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3687,10 +3685,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447430</v>
+        <v>447538</v>
       </c>
       <c r="R32" t="n">
-        <v>6804548</v>
+        <v>6804692</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3723,6 +3721,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3749,10 +3752,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893928</v>
+        <v>129894011</v>
       </c>
       <c r="B33" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3760,42 +3763,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447584</v>
+        <v>447589</v>
       </c>
       <c r="R33" t="n">
-        <v>6804698</v>
+        <v>6804744</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3828,6 +3823,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4260,10 +4260,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894005</v>
+        <v>129893927</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4271,26 +4271,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4298,10 +4303,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447574</v>
+        <v>447561</v>
       </c>
       <c r="R38" t="n">
-        <v>6804491</v>
+        <v>6804628</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4336,18 +4341,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4366,7 +4365,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894001</v>
+        <v>129894005</v>
       </c>
       <c r="B39" t="n">
         <v>79084</v>
@@ -4395,16 +4394,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447491</v>
+        <v>447574</v>
       </c>
       <c r="R39" t="n">
-        <v>6804629</v>
+        <v>6804491</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4439,12 +4441,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4463,54 +4471,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129893962</v>
+        <v>129894001</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447552</v>
+        <v>447491</v>
       </c>
       <c r="R40" t="n">
-        <v>6804720</v>
+        <v>6804629</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4550,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4570,40 +4568,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893927</v>
+        <v>129893962</v>
       </c>
       <c r="B41" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4613,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447561</v>
+        <v>447552</v>
       </c>
       <c r="R41" t="n">
-        <v>6804628</v>
+        <v>6804720</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4657,6 +4656,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894000</v>
+        <v>129893998</v>
       </c>
       <c r="B42" t="n">
         <v>79084</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447442</v>
+        <v>447424</v>
       </c>
       <c r="R42" t="n">
-        <v>6804551</v>
+        <v>6804554</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4746,11 +4746,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4777,10 +4772,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894020</v>
+        <v>129893966</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4788,21 +4783,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4812,10 +4807,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447306</v>
+        <v>447483</v>
       </c>
       <c r="R43" t="n">
-        <v>6804757</v>
+        <v>6804616</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4874,10 +4869,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129893966</v>
+        <v>129894007</v>
       </c>
       <c r="B44" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,21 +4880,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4909,10 +4904,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447483</v>
+        <v>447533</v>
       </c>
       <c r="R44" t="n">
-        <v>6804616</v>
+        <v>6804620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4945,6 +4940,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4971,7 +4971,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893998</v>
+        <v>129894020</v>
       </c>
       <c r="B45" t="n">
         <v>79084</v>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447424</v>
+        <v>447306</v>
       </c>
       <c r="R45" t="n">
-        <v>6804554</v>
+        <v>6804757</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5068,7 +5068,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894007</v>
+        <v>129894000</v>
       </c>
       <c r="B46" t="n">
         <v>79084</v>
@@ -5103,10 +5103,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447533</v>
+        <v>447442</v>
       </c>
       <c r="R46" t="n">
-        <v>6804620</v>
+        <v>6804551</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5374,10 +5374,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893931</v>
+        <v>129893906</v>
       </c>
       <c r="B49" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5385,42 +5385,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447545</v>
+        <v>447569</v>
       </c>
       <c r="R49" t="n">
-        <v>6804718</v>
+        <v>6804584</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5479,10 +5471,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893906</v>
+        <v>129893931</v>
       </c>
       <c r="B50" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5490,34 +5482,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447569</v>
+        <v>447545</v>
       </c>
       <c r="R50" t="n">
-        <v>6804584</v>
+        <v>6804718</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6178,7 +6178,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129894013</v>
+        <v>129894012</v>
       </c>
       <c r="B57" t="n">
         <v>79084</v>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447519</v>
+        <v>447546</v>
       </c>
       <c r="R57" t="n">
-        <v>6804713</v>
+        <v>6804711</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6275,7 +6275,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129894012</v>
+        <v>129894013</v>
       </c>
       <c r="B58" t="n">
         <v>79084</v>
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447546</v>
+        <v>447519</v>
       </c>
       <c r="R58" t="n">
-        <v>6804711</v>
+        <v>6804713</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7704,7 +7704,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129893380</v>
+        <v>129893386</v>
       </c>
       <c r="B72" t="n">
         <v>79084</v>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447464</v>
+        <v>447304</v>
       </c>
       <c r="R72" t="n">
-        <v>6804730</v>
+        <v>6804742</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7775,11 +7775,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7806,7 +7801,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129893386</v>
+        <v>129893380</v>
       </c>
       <c r="B73" t="n">
         <v>79084</v>
@@ -7841,10 +7836,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447304</v>
+        <v>447464</v>
       </c>
       <c r="R73" t="n">
-        <v>6804742</v>
+        <v>6804730</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7877,6 +7872,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9301,54 +9301,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893338</v>
+        <v>129893382</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447531</v>
+        <v>447448</v>
       </c>
       <c r="R88" t="n">
-        <v>6804885</v>
+        <v>6804705</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9389,7 +9380,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9408,45 +9398,54 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893382</v>
+        <v>129893338</v>
       </c>
       <c r="B89" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447448</v>
+        <v>447531</v>
       </c>
       <c r="R89" t="n">
-        <v>6804705</v>
+        <v>6804885</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9487,6 +9486,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9505,10 +9505,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893321</v>
+        <v>129893374</v>
       </c>
       <c r="B90" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9516,42 +9516,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447539</v>
+        <v>447470</v>
       </c>
       <c r="R90" t="n">
-        <v>6804888</v>
+        <v>6805005</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9584,6 +9576,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9610,7 +9607,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893374</v>
+        <v>129893389</v>
       </c>
       <c r="B91" t="n">
         <v>79084</v>
@@ -9645,10 +9642,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447470</v>
+        <v>447326</v>
       </c>
       <c r="R91" t="n">
-        <v>6805005</v>
+        <v>6804648</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9681,11 +9678,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9712,7 +9704,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893389</v>
+        <v>129893388</v>
       </c>
       <c r="B92" t="n">
         <v>79084</v>
@@ -9747,10 +9739,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447326</v>
+        <v>447312</v>
       </c>
       <c r="R92" t="n">
-        <v>6804648</v>
+        <v>6804705</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9809,10 +9801,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893388</v>
+        <v>129893321</v>
       </c>
       <c r="B93" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9820,34 +9812,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447312</v>
+        <v>447539</v>
       </c>
       <c r="R93" t="n">
-        <v>6804705</v>
+        <v>6804888</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129894015</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129893911</v>
       </c>
       <c r="B3" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129893997</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129893947</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129893993</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129894004</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129894008</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129894014</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129893994</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>129894003</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>129894022</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>129893941</v>
       </c>
       <c r="B13" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>129893915</v>
       </c>
       <c r="B14" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>129893901</v>
       </c>
       <c r="B15" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>129893909</v>
       </c>
       <c r="B16" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>129893930</v>
       </c>
       <c r="B17" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>129893904</v>
       </c>
       <c r="B18" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>129893922</v>
       </c>
       <c r="B19" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>129894002</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>129893996</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>129893907</v>
       </c>
       <c r="B22" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>129894048</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2846,45 +2846,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894010</v>
+        <v>129893958</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447599</v>
+        <v>447566</v>
       </c>
       <c r="R24" t="n">
-        <v>6804708</v>
+        <v>6804650</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,6 +2934,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2943,54 +2953,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129893958</v>
+        <v>129894010</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447566</v>
+        <v>447599</v>
       </c>
       <c r="R25" t="n">
-        <v>6804650</v>
+        <v>6804708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,7 +3032,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>129893905</v>
       </c>
       <c r="B26" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>129893960</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>129893903</v>
       </c>
       <c r="B28" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>129893902</v>
       </c>
       <c r="B29" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129893928</v>
+        <v>129894016</v>
       </c>
       <c r="B30" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3459,42 +3459,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447584</v>
+        <v>447444</v>
       </c>
       <c r="R30" t="n">
-        <v>6804698</v>
+        <v>6804723</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,10 +3545,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894016</v>
+        <v>129894009</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,10 +3580,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447444</v>
+        <v>447538</v>
       </c>
       <c r="R31" t="n">
-        <v>6804723</v>
+        <v>6804692</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3624,6 +3616,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3650,10 +3647,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894009</v>
+        <v>129894011</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,10 +3682,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447538</v>
+        <v>447589</v>
       </c>
       <c r="R32" t="n">
-        <v>6804692</v>
+        <v>6804744</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3725,7 +3722,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3752,10 +3749,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894011</v>
+        <v>129893928</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3763,34 +3760,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447589</v>
+        <v>447584</v>
       </c>
       <c r="R33" t="n">
-        <v>6804744</v>
+        <v>6804698</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3823,11 +3828,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3857,7 +3857,7 @@
         <v>129893957</v>
       </c>
       <c r="B34" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>129893908</v>
       </c>
       <c r="B35" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>129893929</v>
       </c>
       <c r="B36" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>129893916</v>
       </c>
       <c r="B37" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>129893927</v>
       </c>
       <c r="B38" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>129894005</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>129894001</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>129893962</v>
       </c>
       <c r="B41" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>129893998</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>129893966</v>
       </c>
       <c r="B43" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>129894007</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4971,10 +4971,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894020</v>
+        <v>129894000</v>
       </c>
       <c r="B45" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447306</v>
+        <v>447442</v>
       </c>
       <c r="R45" t="n">
-        <v>6804757</v>
+        <v>6804551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5042,6 +5042,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5068,10 +5073,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894000</v>
+        <v>129894020</v>
       </c>
       <c r="B46" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5103,10 +5108,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447442</v>
+        <v>447306</v>
       </c>
       <c r="R46" t="n">
-        <v>6804551</v>
+        <v>6804757</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5139,11 +5144,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5173,7 +5173,7 @@
         <v>129893959</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>129893999</v>
       </c>
       <c r="B48" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>129893906</v>
       </c>
       <c r="B49" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>129893931</v>
       </c>
       <c r="B50" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>129894021</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>129894006</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>129893961</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>129893995</v>
       </c>
       <c r="B54" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129893917</v>
+        <v>129893992</v>
       </c>
       <c r="B55" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447580</v>
+        <v>447390</v>
       </c>
       <c r="R55" t="n">
-        <v>6804527</v>
+        <v>6804568</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6050,6 +6050,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6076,10 +6081,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129893992</v>
+        <v>129893917</v>
       </c>
       <c r="B56" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6087,21 +6092,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6111,10 +6116,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447390</v>
+        <v>447580</v>
       </c>
       <c r="R56" t="n">
-        <v>6804568</v>
+        <v>6804527</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6147,11 +6152,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6181,7 +6181,7 @@
         <v>129894012</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>129894013</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>129893910</v>
       </c>
       <c r="B59" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>129893320</v>
       </c>
       <c r="B60" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>129893335</v>
       </c>
       <c r="B61" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>129893327</v>
       </c>
       <c r="B62" t="n">
-        <v>80190</v>
+        <v>80193</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>129893319</v>
       </c>
       <c r="B63" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>129893371</v>
       </c>
       <c r="B64" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>129893373</v>
       </c>
       <c r="B65" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>129893341</v>
       </c>
       <c r="B66" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7193,10 +7193,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893318</v>
+        <v>129893369</v>
       </c>
       <c r="B67" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7204,42 +7204,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447384</v>
+        <v>447459</v>
       </c>
       <c r="R67" t="n">
-        <v>6805028</v>
+        <v>6804815</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7298,10 +7290,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893369</v>
+        <v>129893318</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7309,34 +7301,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447459</v>
+        <v>447384</v>
       </c>
       <c r="R68" t="n">
-        <v>6804815</v>
+        <v>6805028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7398,7 +7398,7 @@
         <v>129893317</v>
       </c>
       <c r="B69" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>129893390</v>
       </c>
       <c r="B70" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>129893337</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7704,10 +7704,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129893386</v>
+        <v>129893380</v>
       </c>
       <c r="B72" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447304</v>
+        <v>447464</v>
       </c>
       <c r="R72" t="n">
-        <v>6804742</v>
+        <v>6804730</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7775,6 +7775,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7801,10 +7806,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129893380</v>
+        <v>129893386</v>
       </c>
       <c r="B73" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7836,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447464</v>
+        <v>447304</v>
       </c>
       <c r="R73" t="n">
-        <v>6804730</v>
+        <v>6804742</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7872,11 +7877,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7906,7 +7906,7 @@
         <v>129893372</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8005,10 +8005,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129893387</v>
+        <v>129893377</v>
       </c>
       <c r="B75" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447301</v>
+        <v>447573</v>
       </c>
       <c r="R75" t="n">
-        <v>6804727</v>
+        <v>6804725</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8102,10 +8102,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129893377</v>
+        <v>129893387</v>
       </c>
       <c r="B76" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447573</v>
+        <v>447301</v>
       </c>
       <c r="R76" t="n">
-        <v>6804725</v>
+        <v>6804727</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8199,54 +8199,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129893336</v>
+        <v>129893379</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447517</v>
+        <v>447553</v>
       </c>
       <c r="R77" t="n">
-        <v>6804963</v>
+        <v>6804766</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8281,13 +8272,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 10 m</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8306,45 +8301,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893379</v>
+        <v>129893336</v>
       </c>
       <c r="B78" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447553</v>
+        <v>447517</v>
       </c>
       <c r="R78" t="n">
-        <v>6804766</v>
+        <v>6804963</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8379,17 +8383,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 10 m</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>129893292</v>
       </c>
       <c r="B79" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>129893376</v>
       </c>
       <c r="B80" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>129893340</v>
       </c>
       <c r="B81" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>129893370</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>129893375</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>129893378</v>
       </c>
       <c r="B84" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>129893293</v>
       </c>
       <c r="B85" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>129893381</v>
       </c>
       <c r="B86" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>129893294</v>
       </c>
       <c r="B87" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>129893382</v>
       </c>
       <c r="B88" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>129893338</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>129893374</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>129893389</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>129893388</v>
       </c>
       <c r="B92" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>129893321</v>
       </c>
       <c r="B93" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893915</v>
+        <v>129893930</v>
       </c>
       <c r="B14" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,34 +1871,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447563</v>
+        <v>447566</v>
       </c>
       <c r="R14" t="n">
-        <v>6804478</v>
+        <v>6804736</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,7 +1965,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893901</v>
+        <v>129893915</v>
       </c>
       <c r="B15" t="n">
         <v>79706</v>
@@ -1992,10 +2000,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447394</v>
+        <v>447563</v>
       </c>
       <c r="R15" t="n">
-        <v>6804571</v>
+        <v>6804478</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,7 +2062,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129893909</v>
+        <v>129893901</v>
       </c>
       <c r="B16" t="n">
         <v>79706</v>
@@ -2089,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447445</v>
+        <v>447394</v>
       </c>
       <c r="R16" t="n">
-        <v>6804759</v>
+        <v>6804571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,10 +2159,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893930</v>
+        <v>129893909</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,42 +2170,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447566</v>
+        <v>447445</v>
       </c>
       <c r="R17" t="n">
-        <v>6804736</v>
+        <v>6804759</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129893907</v>
+        <v>129894010</v>
       </c>
       <c r="B22" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,21 +2663,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447541</v>
+        <v>447599</v>
       </c>
       <c r="R22" t="n">
-        <v>6804663</v>
+        <v>6804708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2749,10 +2749,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894048</v>
+        <v>129893907</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,21 +2760,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447408</v>
+        <v>447541</v>
       </c>
       <c r="R23" t="n">
-        <v>6804651</v>
+        <v>6804663</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,54 +2846,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893958</v>
+        <v>129894048</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447566</v>
+        <v>447408</v>
       </c>
       <c r="R24" t="n">
-        <v>6804650</v>
+        <v>6804651</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2934,7 +2925,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2953,45 +2943,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129894010</v>
+        <v>129893958</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447599</v>
+        <v>447566</v>
       </c>
       <c r="R25" t="n">
-        <v>6804708</v>
+        <v>6804650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3032,6 +3031,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894010</v>
+        <v>129893907</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,21 +2663,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447599</v>
+        <v>447541</v>
       </c>
       <c r="R22" t="n">
-        <v>6804708</v>
+        <v>6804663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2749,10 +2749,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129893907</v>
+        <v>129894048</v>
       </c>
       <c r="B23" t="n">
-        <v>79706</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,21 +2760,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447541</v>
+        <v>447408</v>
       </c>
       <c r="R23" t="n">
-        <v>6804663</v>
+        <v>6804651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,45 +2846,54 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894048</v>
+        <v>129893958</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447408</v>
+        <v>447566</v>
       </c>
       <c r="R24" t="n">
-        <v>6804651</v>
+        <v>6804650</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,6 +2934,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2943,54 +2953,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129893958</v>
+        <v>129894010</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447566</v>
+        <v>447599</v>
       </c>
       <c r="R25" t="n">
-        <v>6804650</v>
+        <v>6804708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,7 +3032,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129893908</v>
+        <v>129893916</v>
       </c>
       <c r="B35" t="n">
-        <v>79706</v>
+        <v>79677</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3972,21 +3972,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447543</v>
+        <v>447402</v>
       </c>
       <c r="R35" t="n">
-        <v>6804684</v>
+        <v>6804565</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4058,10 +4058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129893929</v>
+        <v>129893908</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4069,42 +4069,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447594</v>
+        <v>447543</v>
       </c>
       <c r="R36" t="n">
-        <v>6804744</v>
+        <v>6804684</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4163,10 +4155,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129893916</v>
+        <v>129893929</v>
       </c>
       <c r="B37" t="n">
-        <v>79677</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4174,34 +4166,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447402</v>
+        <v>447594</v>
       </c>
       <c r="R37" t="n">
-        <v>6804565</v>
+        <v>6804744</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129894015</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129893911</v>
       </c>
       <c r="B3" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129893997</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129893947</v>
       </c>
       <c r="B5" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129893993</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129894004</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129894008</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129894014</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129893994</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129894003</v>
+        <v>129893941</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,26 +1564,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1591,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447489</v>
+        <v>447578</v>
       </c>
       <c r="R11" t="n">
-        <v>6804602</v>
+        <v>6804600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1635,7 +1640,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1654,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894022</v>
+        <v>129894003</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1692,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447311</v>
+        <v>447489</v>
       </c>
       <c r="R12" t="n">
-        <v>6804635</v>
+        <v>6804602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,10 +1759,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129893941</v>
+        <v>129894022</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,31 +1770,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1798,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447578</v>
+        <v>447311</v>
       </c>
       <c r="R13" t="n">
-        <v>6804600</v>
+        <v>6804635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,6 +1841,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893930</v>
+        <v>129893915</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1871,42 +1871,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447566</v>
+        <v>447563</v>
       </c>
       <c r="R14" t="n">
-        <v>6804736</v>
+        <v>6804478</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1965,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893915</v>
+        <v>129893901</v>
       </c>
       <c r="B15" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447563</v>
+        <v>447394</v>
       </c>
       <c r="R15" t="n">
-        <v>6804478</v>
+        <v>6804571</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2062,10 +2054,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129893901</v>
+        <v>129893909</v>
       </c>
       <c r="B16" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2097,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447394</v>
+        <v>447445</v>
       </c>
       <c r="R16" t="n">
-        <v>6804571</v>
+        <v>6804759</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2159,10 +2151,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893909</v>
+        <v>129893930</v>
       </c>
       <c r="B17" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,34 +2162,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447445</v>
+        <v>447566</v>
       </c>
       <c r="R17" t="n">
-        <v>6804759</v>
+        <v>6804736</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,45 +2256,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893904</v>
+        <v>129893922</v>
       </c>
       <c r="B18" t="n">
-        <v>79706</v>
+        <v>56930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447491</v>
+        <v>447455</v>
       </c>
       <c r="R18" t="n">
-        <v>6804595</v>
+        <v>6804619</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,53 +2361,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893922</v>
+        <v>129893904</v>
       </c>
       <c r="B19" t="n">
-        <v>56930</v>
+        <v>79707</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447455</v>
+        <v>447491</v>
       </c>
       <c r="R19" t="n">
-        <v>6804619</v>
+        <v>6804595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894002</v>
+        <v>129893996</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447484</v>
+        <v>447398</v>
       </c>
       <c r="R20" t="n">
-        <v>6804623</v>
+        <v>6804577</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129893996</v>
+        <v>129894002</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447398</v>
+        <v>447484</v>
       </c>
       <c r="R21" t="n">
-        <v>6804577</v>
+        <v>6804623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2655,7 +2655,7 @@
         <v>129893907</v>
       </c>
       <c r="B22" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>129894048</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2846,54 +2846,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893958</v>
+        <v>129894010</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447566</v>
+        <v>447599</v>
       </c>
       <c r="R24" t="n">
-        <v>6804650</v>
+        <v>6804708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2934,7 +2925,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2953,45 +2943,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129894010</v>
+        <v>129893958</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447599</v>
+        <v>447566</v>
       </c>
       <c r="R25" t="n">
-        <v>6804708</v>
+        <v>6804650</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3032,6 +3031,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>129893905</v>
       </c>
       <c r="B26" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,45 +3254,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893903</v>
+        <v>129893957</v>
       </c>
       <c r="B28" t="n">
-        <v>79706</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447486</v>
+        <v>447418</v>
       </c>
       <c r="R28" t="n">
-        <v>6804619</v>
+        <v>6804561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3333,6 +3342,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3351,10 +3361,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893902</v>
+        <v>129893903</v>
       </c>
       <c r="B29" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3386,10 +3396,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447430</v>
+        <v>447486</v>
       </c>
       <c r="R29" t="n">
-        <v>6804548</v>
+        <v>6804619</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,10 +3458,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894016</v>
+        <v>129893902</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3459,21 +3469,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3483,10 +3493,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447444</v>
+        <v>447430</v>
       </c>
       <c r="R30" t="n">
-        <v>6804723</v>
+        <v>6804548</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3545,10 +3555,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894009</v>
+        <v>129894016</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3580,10 +3590,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447538</v>
+        <v>447444</v>
       </c>
       <c r="R31" t="n">
-        <v>6804692</v>
+        <v>6804723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3616,11 +3626,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3647,10 +3652,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894011</v>
+        <v>129894009</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3682,10 +3687,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447589</v>
+        <v>447538</v>
       </c>
       <c r="R32" t="n">
-        <v>6804744</v>
+        <v>6804692</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3722,7 +3727,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3749,10 +3754,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893928</v>
+        <v>129894011</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3760,42 +3765,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447584</v>
+        <v>447589</v>
       </c>
       <c r="R33" t="n">
-        <v>6804698</v>
+        <v>6804744</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3828,6 +3825,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,41 +3856,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893957</v>
+        <v>129893928</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3898,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447418</v>
+        <v>447584</v>
       </c>
       <c r="R34" t="n">
-        <v>6804561</v>
+        <v>6804698</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3942,7 +3943,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129893916</v>
+        <v>129893929</v>
       </c>
       <c r="B35" t="n">
-        <v>79677</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3972,34 +3972,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447402</v>
+        <v>447594</v>
       </c>
       <c r="R35" t="n">
-        <v>6804565</v>
+        <v>6804744</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4061,7 +4069,7 @@
         <v>129893908</v>
       </c>
       <c r="B36" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4155,10 +4163,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129893929</v>
+        <v>129893916</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4166,42 +4174,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447594</v>
+        <v>447402</v>
       </c>
       <c r="R37" t="n">
-        <v>6804744</v>
+        <v>6804565</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129893927</v>
+        <v>129894005</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4271,31 +4271,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4303,10 +4298,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447561</v>
+        <v>447574</v>
       </c>
       <c r="R38" t="n">
-        <v>6804628</v>
+        <v>6804491</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4341,12 +4336,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4365,10 +4366,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894005</v>
+        <v>129894001</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4394,19 +4395,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447574</v>
+        <v>447491</v>
       </c>
       <c r="R39" t="n">
-        <v>6804491</v>
+        <v>6804629</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4441,18 +4439,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4471,45 +4463,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894001</v>
+        <v>129893962</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447491</v>
+        <v>447552</v>
       </c>
       <c r="R40" t="n">
-        <v>6804629</v>
+        <v>6804720</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4550,6 +4551,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4568,41 +4570,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893962</v>
+        <v>129893927</v>
       </c>
       <c r="B41" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4612,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447552</v>
+        <v>447561</v>
       </c>
       <c r="R41" t="n">
-        <v>6804720</v>
+        <v>6804628</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4656,7 +4657,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>129893998</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>129893966</v>
       </c>
       <c r="B43" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>129894007</v>
       </c>
       <c r="B44" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>129894000</v>
       </c>
       <c r="B45" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>129894020</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>129893999</v>
       </c>
       <c r="B48" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>129893906</v>
       </c>
       <c r="B49" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5576,45 +5576,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894021</v>
+        <v>129893961</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447330</v>
+        <v>447559</v>
       </c>
       <c r="R51" t="n">
-        <v>6804680</v>
+        <v>6804728</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5649,17 +5658,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5678,10 +5683,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894006</v>
+        <v>129894021</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5713,10 +5718,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447575</v>
+        <v>447330</v>
       </c>
       <c r="R52" t="n">
-        <v>6804539</v>
+        <v>6804680</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5749,6 +5754,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5775,54 +5785,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893961</v>
+        <v>129894006</v>
       </c>
       <c r="B53" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447559</v>
+        <v>447575</v>
       </c>
       <c r="R53" t="n">
-        <v>6804728</v>
+        <v>6804539</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5863,7 +5864,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>129893995</v>
       </c>
       <c r="B54" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>129893992</v>
       </c>
       <c r="B55" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>129893917</v>
       </c>
       <c r="B56" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>129894012</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>129894013</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>129893910</v>
       </c>
       <c r="B59" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6469,40 +6469,41 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893320</v>
+        <v>129893335</v>
       </c>
       <c r="B60" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6512,10 +6513,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447517</v>
+        <v>447503</v>
       </c>
       <c r="R60" t="n">
-        <v>6804957</v>
+        <v>6804998</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,6 +6557,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6574,41 +6576,40 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893335</v>
+        <v>129893320</v>
       </c>
       <c r="B61" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6618,10 +6619,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447503</v>
+        <v>447517</v>
       </c>
       <c r="R61" t="n">
-        <v>6804998</v>
+        <v>6804957</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6663,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>129893327</v>
       </c>
       <c r="B62" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>129893371</v>
       </c>
       <c r="B64" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>129893373</v>
       </c>
       <c r="B65" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>129893341</v>
       </c>
       <c r="B66" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>129893369</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>129893390</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>129893380</v>
       </c>
       <c r="B72" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>129893386</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>129893372</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8005,10 +8005,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129893377</v>
+        <v>129893387</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447573</v>
+        <v>447301</v>
       </c>
       <c r="R75" t="n">
-        <v>6804725</v>
+        <v>6804727</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8102,10 +8102,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129893387</v>
+        <v>129893377</v>
       </c>
       <c r="B76" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447301</v>
+        <v>447573</v>
       </c>
       <c r="R76" t="n">
-        <v>6804727</v>
+        <v>6804725</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8202,7 +8202,7 @@
         <v>129893379</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>129893292</v>
       </c>
       <c r="B79" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>129893376</v>
       </c>
       <c r="B80" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>129893370</v>
       </c>
       <c r="B82" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>129893375</v>
       </c>
       <c r="B83" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>129893378</v>
       </c>
       <c r="B84" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>129893293</v>
       </c>
       <c r="B85" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>129893381</v>
       </c>
       <c r="B86" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>129893294</v>
       </c>
       <c r="B87" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>129893382</v>
       </c>
       <c r="B88" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>129893374</v>
       </c>
       <c r="B90" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>129893389</v>
       </c>
       <c r="B91" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>129893388</v>
       </c>
       <c r="B92" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893997</v>
+        <v>129893947</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447419</v>
+        <v>447580</v>
       </c>
       <c r="R4" t="n">
-        <v>6804565</v>
+        <v>6804504</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893947</v>
+        <v>129893997</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447580</v>
+        <v>447419</v>
       </c>
       <c r="R5" t="n">
-        <v>6804504</v>
+        <v>6804565</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893996</v>
+        <v>129894002</v>
       </c>
       <c r="B20" t="n">
         <v>79088</v>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447398</v>
+        <v>447484</v>
       </c>
       <c r="R20" t="n">
-        <v>6804577</v>
+        <v>6804623</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894002</v>
+        <v>129893996</v>
       </c>
       <c r="B21" t="n">
         <v>79088</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447484</v>
+        <v>447398</v>
       </c>
       <c r="R21" t="n">
-        <v>6804623</v>
+        <v>6804577</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3254,54 +3254,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893957</v>
+        <v>129893903</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447418</v>
+        <v>447486</v>
       </c>
       <c r="R28" t="n">
-        <v>6804561</v>
+        <v>6804619</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3342,7 +3333,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3361,7 +3351,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893903</v>
+        <v>129893902</v>
       </c>
       <c r="B29" t="n">
         <v>79707</v>
@@ -3396,10 +3386,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447486</v>
+        <v>447430</v>
       </c>
       <c r="R29" t="n">
-        <v>6804619</v>
+        <v>6804548</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3458,10 +3448,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129893902</v>
+        <v>129894016</v>
       </c>
       <c r="B30" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3469,21 +3459,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3493,10 +3483,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447430</v>
+        <v>447444</v>
       </c>
       <c r="R30" t="n">
-        <v>6804548</v>
+        <v>6804723</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3555,7 +3545,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894016</v>
+        <v>129894009</v>
       </c>
       <c r="B31" t="n">
         <v>79088</v>
@@ -3590,10 +3580,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447444</v>
+        <v>447538</v>
       </c>
       <c r="R31" t="n">
-        <v>6804723</v>
+        <v>6804692</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3626,6 +3616,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3652,7 +3647,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894009</v>
+        <v>129894011</v>
       </c>
       <c r="B32" t="n">
         <v>79088</v>
@@ -3687,10 +3682,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447538</v>
+        <v>447589</v>
       </c>
       <c r="R32" t="n">
-        <v>6804692</v>
+        <v>6804744</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3727,7 +3722,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3754,10 +3749,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894011</v>
+        <v>129893928</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3765,34 +3760,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447589</v>
+        <v>447584</v>
       </c>
       <c r="R33" t="n">
-        <v>6804744</v>
+        <v>6804698</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3825,11 +3828,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3856,40 +3854,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893928</v>
+        <v>129893957</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3899,10 +3898,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447584</v>
+        <v>447418</v>
       </c>
       <c r="R34" t="n">
-        <v>6804698</v>
+        <v>6804561</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3943,6 +3942,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129893929</v>
+        <v>129893916</v>
       </c>
       <c r="B35" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3972,42 +3972,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447594</v>
+        <v>447402</v>
       </c>
       <c r="R35" t="n">
-        <v>6804744</v>
+        <v>6804565</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4163,10 +4155,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129893916</v>
+        <v>129893929</v>
       </c>
       <c r="B37" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4174,34 +4166,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447402</v>
+        <v>447594</v>
       </c>
       <c r="R37" t="n">
-        <v>6804565</v>
+        <v>6804744</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4260,37 +4260,43 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894005</v>
+        <v>129893962</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4298,10 +4304,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447574</v>
+        <v>447552</v>
       </c>
       <c r="R38" t="n">
-        <v>6804491</v>
+        <v>6804720</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4334,11 +4340,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4366,7 +4367,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894001</v>
+        <v>129894005</v>
       </c>
       <c r="B39" t="n">
         <v>79088</v>
@@ -4395,16 +4396,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447491</v>
+        <v>447574</v>
       </c>
       <c r="R39" t="n">
-        <v>6804629</v>
+        <v>6804491</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4439,12 +4443,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4463,54 +4473,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129893962</v>
+        <v>129894001</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447552</v>
+        <v>447491</v>
       </c>
       <c r="R40" t="n">
-        <v>6804720</v>
+        <v>6804629</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4552,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -9204,45 +9204,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129893294</v>
+        <v>129893338</v>
       </c>
       <c r="B87" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447422</v>
+        <v>447531</v>
       </c>
       <c r="R87" t="n">
-        <v>6805021</v>
+        <v>6804885</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9283,6 +9292,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9301,10 +9311,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893382</v>
+        <v>129893294</v>
       </c>
       <c r="B88" t="n">
-        <v>79088</v>
+        <v>79707</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9312,21 +9322,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9336,10 +9346,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447448</v>
+        <v>447422</v>
       </c>
       <c r="R88" t="n">
-        <v>6804705</v>
+        <v>6805021</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9398,54 +9408,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893338</v>
+        <v>129893382</v>
       </c>
       <c r="B89" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447531</v>
+        <v>447448</v>
       </c>
       <c r="R89" t="n">
-        <v>6804885</v>
+        <v>6804705</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9486,7 +9487,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893947</v>
+        <v>129893997</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447580</v>
+        <v>447419</v>
       </c>
       <c r="R4" t="n">
-        <v>6804504</v>
+        <v>6804565</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893997</v>
+        <v>129893947</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447419</v>
+        <v>447580</v>
       </c>
       <c r="R5" t="n">
-        <v>6804565</v>
+        <v>6804504</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894002</v>
+        <v>129893996</v>
       </c>
       <c r="B20" t="n">
         <v>79088</v>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447484</v>
+        <v>447398</v>
       </c>
       <c r="R20" t="n">
-        <v>6804623</v>
+        <v>6804577</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129893996</v>
+        <v>129894002</v>
       </c>
       <c r="B21" t="n">
         <v>79088</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447398</v>
+        <v>447484</v>
       </c>
       <c r="R21" t="n">
-        <v>6804577</v>
+        <v>6804623</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129893916</v>
+        <v>129893929</v>
       </c>
       <c r="B35" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3972,34 +3972,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447402</v>
+        <v>447594</v>
       </c>
       <c r="R35" t="n">
-        <v>6804565</v>
+        <v>6804744</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,10 +4163,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129893929</v>
+        <v>129893916</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4166,42 +4174,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447594</v>
+        <v>447402</v>
       </c>
       <c r="R37" t="n">
-        <v>6804744</v>
+        <v>6804565</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4260,43 +4260,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129893962</v>
+        <v>129894005</v>
       </c>
       <c r="B38" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4304,10 +4298,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447552</v>
+        <v>447574</v>
       </c>
       <c r="R38" t="n">
-        <v>6804720</v>
+        <v>6804491</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4340,6 +4334,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4367,7 +4366,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894005</v>
+        <v>129894001</v>
       </c>
       <c r="B39" t="n">
         <v>79088</v>
@@ -4396,19 +4395,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447574</v>
+        <v>447491</v>
       </c>
       <c r="R39" t="n">
-        <v>6804491</v>
+        <v>6804629</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4443,18 +4439,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4473,45 +4463,54 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894001</v>
+        <v>129893962</v>
       </c>
       <c r="B40" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447491</v>
+        <v>447552</v>
       </c>
       <c r="R40" t="n">
-        <v>6804629</v>
+        <v>6804720</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4552,6 +4551,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -9204,54 +9204,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129893338</v>
+        <v>129893294</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79707</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447531</v>
+        <v>447422</v>
       </c>
       <c r="R87" t="n">
-        <v>6804885</v>
+        <v>6805021</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9292,7 +9283,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9311,10 +9301,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893294</v>
+        <v>129893382</v>
       </c>
       <c r="B88" t="n">
-        <v>79707</v>
+        <v>79088</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9322,21 +9312,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9346,10 +9336,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447422</v>
+        <v>447448</v>
       </c>
       <c r="R88" t="n">
-        <v>6805021</v>
+        <v>6804705</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9408,45 +9398,54 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893382</v>
+        <v>129893338</v>
       </c>
       <c r="B89" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447448</v>
+        <v>447531</v>
       </c>
       <c r="R89" t="n">
-        <v>6804705</v>
+        <v>6804885</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9487,6 +9486,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894015</v>
+        <v>129893911</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447460</v>
+        <v>447312</v>
       </c>
       <c r="R2" t="n">
-        <v>6804726</v>
+        <v>6804764</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129893911</v>
+        <v>129894015</v>
       </c>
       <c r="B3" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447312</v>
+        <v>447460</v>
       </c>
       <c r="R3" t="n">
-        <v>6804764</v>
+        <v>6804726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>129893997</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129893947</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129893993</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129894004</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129894008</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129894014</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129893994</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>129894003</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>129894022</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893915</v>
+        <v>129893909</v>
       </c>
       <c r="B14" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447563</v>
+        <v>447445</v>
       </c>
       <c r="R14" t="n">
-        <v>6804478</v>
+        <v>6804759</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,10 +1957,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893901</v>
+        <v>129893930</v>
       </c>
       <c r="B15" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1968,34 +1968,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447394</v>
+        <v>447566</v>
       </c>
       <c r="R15" t="n">
-        <v>6804571</v>
+        <v>6804736</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,10 +2062,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129893909</v>
+        <v>129893915</v>
       </c>
       <c r="B16" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2089,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447445</v>
+        <v>447563</v>
       </c>
       <c r="R16" t="n">
-        <v>6804759</v>
+        <v>6804478</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,10 +2159,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893930</v>
+        <v>129893901</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2162,42 +2170,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447566</v>
+        <v>447394</v>
       </c>
       <c r="R17" t="n">
-        <v>6804736</v>
+        <v>6804571</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2256,53 +2256,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893922</v>
+        <v>129893904</v>
       </c>
       <c r="B18" t="n">
-        <v>56930</v>
+        <v>79708</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447455</v>
+        <v>447491</v>
       </c>
       <c r="R18" t="n">
-        <v>6804619</v>
+        <v>6804595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,45 +2353,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893904</v>
+        <v>129893922</v>
       </c>
       <c r="B19" t="n">
-        <v>79707</v>
+        <v>56930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447491</v>
+        <v>447455</v>
       </c>
       <c r="R19" t="n">
-        <v>6804595</v>
+        <v>6804619</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129893996</v>
+        <v>129894002</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447398</v>
+        <v>447484</v>
       </c>
       <c r="R20" t="n">
-        <v>6804577</v>
+        <v>6804623</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894002</v>
+        <v>129893996</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447484</v>
+        <v>447398</v>
       </c>
       <c r="R21" t="n">
-        <v>6804623</v>
+        <v>6804577</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2655,7 +2655,7 @@
         <v>129893907</v>
       </c>
       <c r="B22" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>129894048</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>129894010</v>
       </c>
       <c r="B24" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>129893905</v>
       </c>
       <c r="B26" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893903</v>
+        <v>129893928</v>
       </c>
       <c r="B28" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3265,34 +3265,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447486</v>
+        <v>447584</v>
       </c>
       <c r="R28" t="n">
-        <v>6804619</v>
+        <v>6804698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3351,10 +3359,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893902</v>
+        <v>129893903</v>
       </c>
       <c r="B29" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3386,10 +3394,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447430</v>
+        <v>447486</v>
       </c>
       <c r="R29" t="n">
-        <v>6804548</v>
+        <v>6804619</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3451,7 +3459,7 @@
         <v>129894016</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3548,7 +3556,7 @@
         <v>129894009</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3647,45 +3655,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894011</v>
+        <v>129893957</v>
       </c>
       <c r="B32" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447589</v>
+        <v>447418</v>
       </c>
       <c r="R32" t="n">
-        <v>6804744</v>
+        <v>6804561</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3720,17 +3737,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3749,10 +3762,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893928</v>
+        <v>129893902</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3760,42 +3773,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447584</v>
+        <v>447430</v>
       </c>
       <c r="R33" t="n">
-        <v>6804698</v>
+        <v>6804548</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3854,54 +3859,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893957</v>
+        <v>129894011</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447418</v>
+        <v>447589</v>
       </c>
       <c r="R34" t="n">
-        <v>6804561</v>
+        <v>6804744</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3936,13 +3932,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4069,7 +4069,7 @@
         <v>129893908</v>
       </c>
       <c r="B36" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>129893916</v>
       </c>
       <c r="B37" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894005</v>
+        <v>129893927</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4271,26 +4271,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4298,10 +4303,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447574</v>
+        <v>447561</v>
       </c>
       <c r="R38" t="n">
-        <v>6804491</v>
+        <v>6804628</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4336,18 +4341,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4366,10 +4365,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894001</v>
+        <v>129894005</v>
       </c>
       <c r="B39" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4395,16 +4394,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447491</v>
+        <v>447574</v>
       </c>
       <c r="R39" t="n">
-        <v>6804629</v>
+        <v>6804491</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4439,12 +4441,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4463,54 +4471,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129893962</v>
+        <v>129894001</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447552</v>
+        <v>447491</v>
       </c>
       <c r="R40" t="n">
-        <v>6804720</v>
+        <v>6804629</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4550,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4570,40 +4568,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893927</v>
+        <v>129893962</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4613,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447561</v>
+        <v>447552</v>
       </c>
       <c r="R41" t="n">
-        <v>6804628</v>
+        <v>6804720</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4657,6 +4656,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4675,45 +4675,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129893998</v>
+        <v>129893959</v>
       </c>
       <c r="B42" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447424</v>
+        <v>447540</v>
       </c>
       <c r="R42" t="n">
-        <v>6804554</v>
+        <v>6804664</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4754,6 +4763,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4772,10 +4782,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129893966</v>
+        <v>129893998</v>
       </c>
       <c r="B43" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4783,21 +4793,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4807,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447483</v>
+        <v>447424</v>
       </c>
       <c r="R43" t="n">
-        <v>6804616</v>
+        <v>6804554</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4869,10 +4879,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894007</v>
+        <v>129893966</v>
       </c>
       <c r="B44" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4880,21 +4890,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4904,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447533</v>
+        <v>447483</v>
       </c>
       <c r="R44" t="n">
-        <v>6804620</v>
+        <v>6804616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4940,11 +4950,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4971,10 +4976,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894000</v>
+        <v>129894007</v>
       </c>
       <c r="B45" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5006,10 +5011,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447442</v>
+        <v>447533</v>
       </c>
       <c r="R45" t="n">
-        <v>6804551</v>
+        <v>6804620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5046,7 +5051,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5073,10 +5078,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894020</v>
+        <v>129894000</v>
       </c>
       <c r="B46" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5108,10 +5113,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447306</v>
+        <v>447442</v>
       </c>
       <c r="R46" t="n">
-        <v>6804757</v>
+        <v>6804551</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5144,6 +5149,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5170,54 +5180,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893959</v>
+        <v>129894020</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447540</v>
+        <v>447306</v>
       </c>
       <c r="R47" t="n">
-        <v>6804664</v>
+        <v>6804757</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5258,7 +5259,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5280,7 +5280,7 @@
         <v>129893999</v>
       </c>
       <c r="B48" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5374,10 +5374,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893906</v>
+        <v>129893931</v>
       </c>
       <c r="B49" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5385,34 +5385,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447569</v>
+        <v>447545</v>
       </c>
       <c r="R49" t="n">
-        <v>6804584</v>
+        <v>6804718</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5471,10 +5479,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893931</v>
+        <v>129893906</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5482,42 +5490,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447545</v>
+        <v>447569</v>
       </c>
       <c r="R50" t="n">
-        <v>6804718</v>
+        <v>6804584</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5576,54 +5576,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893961</v>
+        <v>129894021</v>
       </c>
       <c r="B51" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447559</v>
+        <v>447330</v>
       </c>
       <c r="R51" t="n">
-        <v>6804728</v>
+        <v>6804680</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,13 +5649,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5683,10 +5678,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894021</v>
+        <v>129894006</v>
       </c>
       <c r="B52" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5718,10 +5713,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447330</v>
+        <v>447575</v>
       </c>
       <c r="R52" t="n">
-        <v>6804680</v>
+        <v>6804539</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5754,11 +5749,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5785,45 +5775,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129894006</v>
+        <v>129893961</v>
       </c>
       <c r="B53" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447575</v>
+        <v>447559</v>
       </c>
       <c r="R53" t="n">
-        <v>6804539</v>
+        <v>6804728</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5864,6 +5863,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>129893995</v>
       </c>
       <c r="B54" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>129893992</v>
       </c>
       <c r="B55" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>129893917</v>
       </c>
       <c r="B56" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129894012</v>
+        <v>129894013</v>
       </c>
       <c r="B57" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447546</v>
+        <v>447519</v>
       </c>
       <c r="R57" t="n">
-        <v>6804711</v>
+        <v>6804713</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6275,10 +6275,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129894013</v>
+        <v>129893910</v>
       </c>
       <c r="B58" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6286,21 +6286,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447519</v>
+        <v>447424</v>
       </c>
       <c r="R58" t="n">
-        <v>6804713</v>
+        <v>6804723</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893910</v>
+        <v>129894012</v>
       </c>
       <c r="B59" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447424</v>
+        <v>447546</v>
       </c>
       <c r="R59" t="n">
-        <v>6804723</v>
+        <v>6804711</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6469,41 +6469,40 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893335</v>
+        <v>129893320</v>
       </c>
       <c r="B60" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6513,10 +6512,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447503</v>
+        <v>447517</v>
       </c>
       <c r="R60" t="n">
-        <v>6804998</v>
+        <v>6804957</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6557,7 +6556,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6576,40 +6574,41 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893320</v>
+        <v>129893335</v>
       </c>
       <c r="B61" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6619,10 +6618,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447517</v>
+        <v>447503</v>
       </c>
       <c r="R61" t="n">
-        <v>6804957</v>
+        <v>6804998</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6663,6 +6662,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>129893327</v>
       </c>
       <c r="B62" t="n">
-        <v>80194</v>
+        <v>80195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>129893371</v>
       </c>
       <c r="B64" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>129893373</v>
       </c>
       <c r="B65" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7087,10 +7087,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893341</v>
+        <v>129893318</v>
       </c>
       <c r="B66" t="n">
-        <v>80193</v>
+        <v>57737</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7098,26 +7098,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7125,10 +7130,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447580</v>
+        <v>447384</v>
       </c>
       <c r="R66" t="n">
-        <v>6804735</v>
+        <v>6805028</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7163,18 +7168,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7193,10 +7192,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893369</v>
+        <v>129893341</v>
       </c>
       <c r="B67" t="n">
-        <v>79088</v>
+        <v>80194</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7204,34 +7203,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447459</v>
+        <v>447580</v>
       </c>
       <c r="R67" t="n">
-        <v>6804815</v>
+        <v>6804735</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7266,12 +7268,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7290,10 +7298,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893318</v>
+        <v>129893369</v>
       </c>
       <c r="B68" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7301,42 +7309,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447384</v>
+        <v>447459</v>
       </c>
       <c r="R68" t="n">
-        <v>6805028</v>
+        <v>6804815</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7503,7 +7503,7 @@
         <v>129893390</v>
       </c>
       <c r="B70" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>129893380</v>
       </c>
       <c r="B72" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>129893386</v>
       </c>
       <c r="B73" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>129893372</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>129893387</v>
       </c>
       <c r="B75" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>129893377</v>
       </c>
       <c r="B76" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>129893379</v>
       </c>
       <c r="B77" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>129893292</v>
       </c>
       <c r="B79" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8505,45 +8505,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893376</v>
+        <v>129893340</v>
       </c>
       <c r="B80" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447576</v>
+        <v>447459</v>
       </c>
       <c r="R80" t="n">
-        <v>6804770</v>
+        <v>6804731</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8584,6 +8593,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8602,54 +8612,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893340</v>
+        <v>129893376</v>
       </c>
       <c r="B81" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447459</v>
+        <v>447576</v>
       </c>
       <c r="R81" t="n">
-        <v>6804731</v>
+        <v>6804770</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8690,7 +8691,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>129893370</v>
       </c>
       <c r="B82" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>129893375</v>
       </c>
       <c r="B83" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>129893378</v>
       </c>
       <c r="B84" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>129893293</v>
       </c>
       <c r="B85" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>129893381</v>
       </c>
       <c r="B86" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9204,45 +9204,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129893294</v>
+        <v>129893338</v>
       </c>
       <c r="B87" t="n">
-        <v>79707</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447422</v>
+        <v>447531</v>
       </c>
       <c r="R87" t="n">
-        <v>6805021</v>
+        <v>6804885</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9283,6 +9292,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9301,10 +9311,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893382</v>
+        <v>129893294</v>
       </c>
       <c r="B88" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9312,21 +9322,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9336,10 +9346,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447448</v>
+        <v>447422</v>
       </c>
       <c r="R88" t="n">
-        <v>6804705</v>
+        <v>6805021</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9398,54 +9408,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893338</v>
+        <v>129893382</v>
       </c>
       <c r="B89" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447531</v>
+        <v>447448</v>
       </c>
       <c r="R89" t="n">
-        <v>6804885</v>
+        <v>6804705</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9486,7 +9487,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9505,10 +9505,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893374</v>
+        <v>129893321</v>
       </c>
       <c r="B90" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9516,34 +9516,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447470</v>
+        <v>447539</v>
       </c>
       <c r="R90" t="n">
-        <v>6805005</v>
+        <v>6804888</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9576,11 +9584,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9607,10 +9610,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893389</v>
+        <v>129893374</v>
       </c>
       <c r="B91" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9642,10 +9645,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447326</v>
+        <v>447470</v>
       </c>
       <c r="R91" t="n">
-        <v>6804648</v>
+        <v>6805005</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9678,6 +9681,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9704,10 +9712,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893388</v>
+        <v>129893389</v>
       </c>
       <c r="B92" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9739,10 +9747,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447312</v>
+        <v>447326</v>
       </c>
       <c r="R92" t="n">
-        <v>6804705</v>
+        <v>6804648</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9801,10 +9809,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893321</v>
+        <v>129893388</v>
       </c>
       <c r="B93" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9812,42 +9820,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447539</v>
+        <v>447312</v>
       </c>
       <c r="R93" t="n">
-        <v>6804888</v>
+        <v>6804705</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893994</v>
+        <v>129894014</v>
       </c>
       <c r="B9" t="n">
         <v>79095</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447393</v>
+        <v>447482</v>
       </c>
       <c r="R9" t="n">
-        <v>6804563</v>
+        <v>6804743</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129894014</v>
+        <v>129893994</v>
       </c>
       <c r="B10" t="n">
         <v>79095</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447482</v>
+        <v>447393</v>
       </c>
       <c r="R10" t="n">
-        <v>6804743</v>
+        <v>6804563</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894009</v>
+        <v>129893928</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3265,34 +3265,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447538</v>
+        <v>447584</v>
       </c>
       <c r="R28" t="n">
-        <v>6804692</v>
+        <v>6804698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3325,11 +3333,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3356,7 +3359,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894016</v>
+        <v>129894009</v>
       </c>
       <c r="B29" t="n">
         <v>79095</v>
@@ -3391,10 +3394,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447444</v>
+        <v>447538</v>
       </c>
       <c r="R29" t="n">
-        <v>6804723</v>
+        <v>6804692</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,6 +3430,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3453,10 +3461,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129893902</v>
+        <v>129894016</v>
       </c>
       <c r="B30" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3464,21 +3472,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3488,10 +3496,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447430</v>
+        <v>447444</v>
       </c>
       <c r="R30" t="n">
-        <v>6804548</v>
+        <v>6804723</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3550,7 +3558,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129893903</v>
+        <v>129893902</v>
       </c>
       <c r="B31" t="n">
         <v>79714</v>
@@ -3585,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447486</v>
+        <v>447430</v>
       </c>
       <c r="R31" t="n">
-        <v>6804619</v>
+        <v>6804548</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3647,10 +3655,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894011</v>
+        <v>129893903</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3658,21 +3666,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3682,10 +3690,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447589</v>
+        <v>447486</v>
       </c>
       <c r="R32" t="n">
-        <v>6804744</v>
+        <v>6804619</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3718,11 +3726,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3749,54 +3752,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893957</v>
+        <v>129894011</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447418</v>
+        <v>447589</v>
       </c>
       <c r="R33" t="n">
-        <v>6804561</v>
+        <v>6804744</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3831,13 +3825,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3856,40 +3854,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893928</v>
+        <v>129893957</v>
       </c>
       <c r="B34" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3899,10 +3898,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447584</v>
+        <v>447418</v>
       </c>
       <c r="R34" t="n">
-        <v>6804698</v>
+        <v>6804561</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3943,6 +3942,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4675,45 +4675,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894000</v>
+        <v>129893959</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447442</v>
+        <v>447540</v>
       </c>
       <c r="R42" t="n">
-        <v>6804551</v>
+        <v>6804664</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4748,17 +4757,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4777,7 +4782,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894007</v>
+        <v>129894000</v>
       </c>
       <c r="B43" t="n">
         <v>79095</v>
@@ -4812,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447533</v>
+        <v>447442</v>
       </c>
       <c r="R43" t="n">
-        <v>6804620</v>
+        <v>6804551</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4852,7 +4857,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4879,7 +4884,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129893998</v>
+        <v>129894007</v>
       </c>
       <c r="B44" t="n">
         <v>79095</v>
@@ -4914,10 +4919,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447424</v>
+        <v>447533</v>
       </c>
       <c r="R44" t="n">
-        <v>6804554</v>
+        <v>6804620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4950,6 +4955,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4976,7 +4986,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894020</v>
+        <v>129893998</v>
       </c>
       <c r="B45" t="n">
         <v>79095</v>
@@ -5011,10 +5021,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447306</v>
+        <v>447424</v>
       </c>
       <c r="R45" t="n">
-        <v>6804757</v>
+        <v>6804554</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5073,10 +5083,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893966</v>
+        <v>129894020</v>
       </c>
       <c r="B46" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5084,21 +5094,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5108,10 +5118,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447483</v>
+        <v>447306</v>
       </c>
       <c r="R46" t="n">
-        <v>6804616</v>
+        <v>6804757</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5170,54 +5180,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893959</v>
+        <v>129893966</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>78852</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447540</v>
+        <v>447483</v>
       </c>
       <c r="R47" t="n">
-        <v>6804664</v>
+        <v>6804616</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5258,7 +5259,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5576,54 +5576,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893961</v>
+        <v>129894021</v>
       </c>
       <c r="B51" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447559</v>
+        <v>447330</v>
       </c>
       <c r="R51" t="n">
-        <v>6804728</v>
+        <v>6804680</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,13 +5649,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5683,7 +5678,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894021</v>
+        <v>129894006</v>
       </c>
       <c r="B52" t="n">
         <v>79095</v>
@@ -5718,10 +5713,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447330</v>
+        <v>447575</v>
       </c>
       <c r="R52" t="n">
-        <v>6804680</v>
+        <v>6804539</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5754,11 +5749,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5785,45 +5775,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129894006</v>
+        <v>129893961</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447575</v>
+        <v>447559</v>
       </c>
       <c r="R53" t="n">
-        <v>6804539</v>
+        <v>6804728</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5864,6 +5863,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -8199,54 +8199,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129893336</v>
+        <v>129893379</v>
       </c>
       <c r="B77" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447517</v>
+        <v>447553</v>
       </c>
       <c r="R77" t="n">
-        <v>6804963</v>
+        <v>6804766</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8281,13 +8272,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 10 m</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8306,45 +8301,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893379</v>
+        <v>129893336</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447553</v>
+        <v>447517</v>
       </c>
       <c r="R78" t="n">
-        <v>6804766</v>
+        <v>6804963</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8379,17 +8383,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 10 m</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -2256,53 +2256,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893922</v>
+        <v>129893904</v>
       </c>
       <c r="B18" t="n">
-        <v>56931</v>
+        <v>79714</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447455</v>
+        <v>447491</v>
       </c>
       <c r="R18" t="n">
-        <v>6804619</v>
+        <v>6804595</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2361,45 +2353,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893904</v>
+        <v>129893922</v>
       </c>
       <c r="B19" t="n">
-        <v>79714</v>
+        <v>56931</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447491</v>
+        <v>447455</v>
       </c>
       <c r="R19" t="n">
-        <v>6804595</v>
+        <v>6804619</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894005</v>
+        <v>129893927</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4271,26 +4271,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4298,10 +4303,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447574</v>
+        <v>447561</v>
       </c>
       <c r="R38" t="n">
-        <v>6804491</v>
+        <v>6804628</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4336,18 +4341,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4366,7 +4365,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894001</v>
+        <v>129894005</v>
       </c>
       <c r="B39" t="n">
         <v>79095</v>
@@ -4395,16 +4394,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447491</v>
+        <v>447574</v>
       </c>
       <c r="R39" t="n">
-        <v>6804629</v>
+        <v>6804491</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4439,12 +4441,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4463,54 +4471,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129893962</v>
+        <v>129894001</v>
       </c>
       <c r="B40" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447552</v>
+        <v>447491</v>
       </c>
       <c r="R40" t="n">
-        <v>6804720</v>
+        <v>6804629</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4550,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4570,40 +4568,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893927</v>
+        <v>129893962</v>
       </c>
       <c r="B41" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4613,10 +4612,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447561</v>
+        <v>447552</v>
       </c>
       <c r="R41" t="n">
-        <v>6804628</v>
+        <v>6804720</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4657,6 +4656,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5576,45 +5576,54 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894021</v>
+        <v>129893961</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447330</v>
+        <v>447559</v>
       </c>
       <c r="R51" t="n">
-        <v>6804680</v>
+        <v>6804728</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5649,17 +5658,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5678,7 +5683,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894006</v>
+        <v>129894021</v>
       </c>
       <c r="B52" t="n">
         <v>79095</v>
@@ -5713,10 +5718,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447575</v>
+        <v>447330</v>
       </c>
       <c r="R52" t="n">
-        <v>6804539</v>
+        <v>6804680</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5749,6 +5754,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5775,54 +5785,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893961</v>
+        <v>129894006</v>
       </c>
       <c r="B53" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447559</v>
+        <v>447575</v>
       </c>
       <c r="R53" t="n">
-        <v>6804728</v>
+        <v>6804539</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5863,7 +5864,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -9204,45 +9204,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129893294</v>
+        <v>129893338</v>
       </c>
       <c r="B87" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447422</v>
+        <v>447531</v>
       </c>
       <c r="R87" t="n">
-        <v>6805021</v>
+        <v>6804885</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9283,6 +9292,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9301,10 +9311,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893382</v>
+        <v>129893294</v>
       </c>
       <c r="B88" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9312,21 +9322,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9336,10 +9346,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447448</v>
+        <v>447422</v>
       </c>
       <c r="R88" t="n">
-        <v>6804705</v>
+        <v>6805021</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9398,54 +9408,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893338</v>
+        <v>129893382</v>
       </c>
       <c r="B89" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447531</v>
+        <v>447448</v>
       </c>
       <c r="R89" t="n">
-        <v>6804885</v>
+        <v>6804705</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9486,7 +9487,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893947</v>
+        <v>129893997</v>
       </c>
       <c r="B4" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447580</v>
+        <v>447419</v>
       </c>
       <c r="R4" t="n">
-        <v>6804504</v>
+        <v>6804565</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893997</v>
+        <v>129893947</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447419</v>
+        <v>447580</v>
       </c>
       <c r="R5" t="n">
-        <v>6804565</v>
+        <v>6804504</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129894004</v>
+        <v>129893993</v>
       </c>
       <c r="B6" t="n">
         <v>79095</v>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447553</v>
+        <v>447392</v>
       </c>
       <c r="R6" t="n">
-        <v>6804480</v>
+        <v>6804569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893993</v>
+        <v>129894004</v>
       </c>
       <c r="B7" t="n">
         <v>79095</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447392</v>
+        <v>447553</v>
       </c>
       <c r="R7" t="n">
-        <v>6804569</v>
+        <v>6804480</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129893941</v>
+        <v>129894003</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,31 +1564,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1596,10 +1591,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447578</v>
+        <v>447489</v>
       </c>
       <c r="R11" t="n">
-        <v>6804600</v>
+        <v>6804602</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1640,6 +1635,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1658,7 +1654,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894003</v>
+        <v>129894022</v>
       </c>
       <c r="B12" t="n">
         <v>79095</v>
@@ -1696,10 +1692,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447489</v>
+        <v>447311</v>
       </c>
       <c r="R12" t="n">
-        <v>6804602</v>
+        <v>6804635</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1759,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894022</v>
+        <v>129893941</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1770,26 +1766,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1797,10 +1798,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447311</v>
+        <v>447578</v>
       </c>
       <c r="R13" t="n">
-        <v>6804635</v>
+        <v>6804600</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1841,7 +1842,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1860,7 +1860,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893909</v>
+        <v>129893915</v>
       </c>
       <c r="B14" t="n">
         <v>79714</v>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447445</v>
+        <v>447563</v>
       </c>
       <c r="R14" t="n">
-        <v>6804759</v>
+        <v>6804478</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129893915</v>
+        <v>129893909</v>
       </c>
       <c r="B16" t="n">
         <v>79714</v>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447563</v>
+        <v>447445</v>
       </c>
       <c r="R16" t="n">
-        <v>6804478</v>
+        <v>6804759</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2652,10 +2652,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129893907</v>
+        <v>129894048</v>
       </c>
       <c r="B22" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2663,21 +2663,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447541</v>
+        <v>447408</v>
       </c>
       <c r="R22" t="n">
-        <v>6804663</v>
+        <v>6804651</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2749,7 +2749,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894048</v>
+        <v>129894010</v>
       </c>
       <c r="B23" t="n">
         <v>79095</v>
@@ -2784,10 +2784,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447408</v>
+        <v>447599</v>
       </c>
       <c r="R23" t="n">
-        <v>6804651</v>
+        <v>6804708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894010</v>
+        <v>129893907</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2857,21 +2857,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447599</v>
+        <v>447541</v>
       </c>
       <c r="R24" t="n">
-        <v>6804708</v>
+        <v>6804663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3359,7 +3359,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894009</v>
+        <v>129894016</v>
       </c>
       <c r="B29" t="n">
         <v>79095</v>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447538</v>
+        <v>447444</v>
       </c>
       <c r="R29" t="n">
-        <v>6804692</v>
+        <v>6804723</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3430,11 +3430,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3461,7 +3456,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894016</v>
+        <v>129894009</v>
       </c>
       <c r="B30" t="n">
         <v>79095</v>
@@ -3496,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447444</v>
+        <v>447538</v>
       </c>
       <c r="R30" t="n">
-        <v>6804723</v>
+        <v>6804692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3532,6 +3527,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3558,10 +3558,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129893902</v>
+        <v>129894011</v>
       </c>
       <c r="B31" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447430</v>
+        <v>447589</v>
       </c>
       <c r="R31" t="n">
-        <v>6804548</v>
+        <v>6804744</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3629,6 +3629,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3752,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894011</v>
+        <v>129893902</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3763,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3787,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447589</v>
+        <v>447430</v>
       </c>
       <c r="R33" t="n">
-        <v>6804744</v>
+        <v>6804548</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3823,11 +3828,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3961,10 +3961,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129893929</v>
+        <v>129893908</v>
       </c>
       <c r="B35" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3972,42 +3972,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447594</v>
+        <v>447543</v>
       </c>
       <c r="R35" t="n">
-        <v>6804744</v>
+        <v>6804684</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4066,10 +4058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129893916</v>
+        <v>129893929</v>
       </c>
       <c r="B36" t="n">
-        <v>79685</v>
+        <v>57738</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4077,34 +4069,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447402</v>
+        <v>447594</v>
       </c>
       <c r="R36" t="n">
-        <v>6804565</v>
+        <v>6804744</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4163,10 +4163,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129893908</v>
+        <v>129893916</v>
       </c>
       <c r="B37" t="n">
-        <v>79714</v>
+        <v>79685</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4198,10 +4198,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447543</v>
+        <v>447402</v>
       </c>
       <c r="R37" t="n">
-        <v>6804684</v>
+        <v>6804565</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129893927</v>
+        <v>129894005</v>
       </c>
       <c r="B38" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4271,31 +4271,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4303,10 +4298,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447561</v>
+        <v>447574</v>
       </c>
       <c r="R38" t="n">
-        <v>6804628</v>
+        <v>6804491</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4341,12 +4336,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4365,7 +4366,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894005</v>
+        <v>129894001</v>
       </c>
       <c r="B39" t="n">
         <v>79095</v>
@@ -4394,19 +4395,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447574</v>
+        <v>447491</v>
       </c>
       <c r="R39" t="n">
-        <v>6804491</v>
+        <v>6804629</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4441,18 +4439,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4471,10 +4463,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129894001</v>
+        <v>129893927</v>
       </c>
       <c r="B40" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4482,34 +4474,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447491</v>
+        <v>447561</v>
       </c>
       <c r="R40" t="n">
-        <v>6804629</v>
+        <v>6804628</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4675,54 +4675,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129893959</v>
+        <v>129893998</v>
       </c>
       <c r="B42" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447540</v>
+        <v>447424</v>
       </c>
       <c r="R42" t="n">
-        <v>6804664</v>
+        <v>6804554</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4763,7 +4754,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4782,7 +4772,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894000</v>
+        <v>129894007</v>
       </c>
       <c r="B43" t="n">
         <v>79095</v>
@@ -4817,10 +4807,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447442</v>
+        <v>447533</v>
       </c>
       <c r="R43" t="n">
-        <v>6804551</v>
+        <v>6804620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4857,7 +4847,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4884,7 +4874,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894007</v>
+        <v>129894000</v>
       </c>
       <c r="B44" t="n">
         <v>79095</v>
@@ -4919,10 +4909,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447533</v>
+        <v>447442</v>
       </c>
       <c r="R44" t="n">
-        <v>6804620</v>
+        <v>6804551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4959,7 +4949,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4986,7 +4976,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893998</v>
+        <v>129894020</v>
       </c>
       <c r="B45" t="n">
         <v>79095</v>
@@ -5021,10 +5011,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447424</v>
+        <v>447306</v>
       </c>
       <c r="R45" t="n">
-        <v>6804554</v>
+        <v>6804757</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5083,45 +5073,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894020</v>
+        <v>129893959</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447306</v>
+        <v>447540</v>
       </c>
       <c r="R46" t="n">
-        <v>6804757</v>
+        <v>6804664</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5162,6 +5161,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5374,10 +5374,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893931</v>
+        <v>129893906</v>
       </c>
       <c r="B49" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5385,42 +5385,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447545</v>
+        <v>447569</v>
       </c>
       <c r="R49" t="n">
-        <v>6804718</v>
+        <v>6804584</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5479,10 +5471,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893906</v>
+        <v>129893931</v>
       </c>
       <c r="B50" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5490,34 +5482,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447569</v>
+        <v>447545</v>
       </c>
       <c r="R50" t="n">
-        <v>6804584</v>
+        <v>6804718</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6178,7 +6178,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129894013</v>
+        <v>129894012</v>
       </c>
       <c r="B57" t="n">
         <v>79095</v>
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>447519</v>
+        <v>447546</v>
       </c>
       <c r="R57" t="n">
-        <v>6804713</v>
+        <v>6804711</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6275,10 +6275,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129893910</v>
+        <v>129894013</v>
       </c>
       <c r="B58" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6286,21 +6286,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447424</v>
+        <v>447519</v>
       </c>
       <c r="R58" t="n">
-        <v>6804723</v>
+        <v>6804713</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6372,10 +6372,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129894012</v>
+        <v>129893910</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6383,21 +6383,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447546</v>
+        <v>447424</v>
       </c>
       <c r="R59" t="n">
-        <v>6804711</v>
+        <v>6804723</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7087,10 +7087,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893318</v>
+        <v>129893369</v>
       </c>
       <c r="B66" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7098,42 +7098,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447384</v>
+        <v>447459</v>
       </c>
       <c r="R66" t="n">
-        <v>6805028</v>
+        <v>6804815</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7298,10 +7290,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893369</v>
+        <v>129893318</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7309,34 +7301,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447459</v>
+        <v>447384</v>
       </c>
       <c r="R68" t="n">
-        <v>6804815</v>
+        <v>6805028</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7704,7 +7704,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129893386</v>
+        <v>129893380</v>
       </c>
       <c r="B72" t="n">
         <v>79095</v>
@@ -7739,10 +7739,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447304</v>
+        <v>447464</v>
       </c>
       <c r="R72" t="n">
-        <v>6804742</v>
+        <v>6804730</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7775,6 +7775,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7801,7 +7806,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129893380</v>
+        <v>129893386</v>
       </c>
       <c r="B73" t="n">
         <v>79095</v>
@@ -7836,10 +7841,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447464</v>
+        <v>447304</v>
       </c>
       <c r="R73" t="n">
-        <v>6804730</v>
+        <v>6804742</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7872,11 +7877,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8811,7 +8811,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129893378</v>
+        <v>129893375</v>
       </c>
       <c r="B83" t="n">
         <v>79095</v>
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447564</v>
+        <v>447518</v>
       </c>
       <c r="R83" t="n">
-        <v>6804749</v>
+        <v>6804907</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8882,6 +8882,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8908,7 +8913,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129893375</v>
+        <v>129893378</v>
       </c>
       <c r="B84" t="n">
         <v>79095</v>
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447518</v>
+        <v>447564</v>
       </c>
       <c r="R84" t="n">
-        <v>6804907</v>
+        <v>6804749</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8979,11 +8984,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9010,10 +9010,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893293</v>
+        <v>129893381</v>
       </c>
       <c r="B85" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9021,21 +9021,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447420</v>
+        <v>447451</v>
       </c>
       <c r="R85" t="n">
-        <v>6804795</v>
+        <v>6804727</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9107,10 +9107,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893381</v>
+        <v>129893293</v>
       </c>
       <c r="B86" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9118,21 +9118,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9142,10 +9142,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447451</v>
+        <v>447420</v>
       </c>
       <c r="R86" t="n">
-        <v>6804727</v>
+        <v>6804795</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9204,54 +9204,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129893338</v>
+        <v>129893382</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447531</v>
+        <v>447448</v>
       </c>
       <c r="R87" t="n">
-        <v>6804885</v>
+        <v>6804705</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9292,7 +9283,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9311,45 +9301,54 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893294</v>
+        <v>129893338</v>
       </c>
       <c r="B88" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447422</v>
+        <v>447531</v>
       </c>
       <c r="R88" t="n">
-        <v>6805021</v>
+        <v>6804885</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9390,6 +9389,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9408,10 +9408,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893382</v>
+        <v>129893294</v>
       </c>
       <c r="B89" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9419,21 +9419,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447448</v>
+        <v>447422</v>
       </c>
       <c r="R89" t="n">
-        <v>6804705</v>
+        <v>6805021</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9505,10 +9505,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893321</v>
+        <v>129893374</v>
       </c>
       <c r="B90" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9516,42 +9516,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447539</v>
+        <v>447470</v>
       </c>
       <c r="R90" t="n">
-        <v>6804888</v>
+        <v>6805005</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9584,6 +9576,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9610,7 +9607,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893388</v>
+        <v>129893389</v>
       </c>
       <c r="B91" t="n">
         <v>79095</v>
@@ -9645,10 +9642,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447312</v>
+        <v>447326</v>
       </c>
       <c r="R91" t="n">
-        <v>6804705</v>
+        <v>6804648</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9707,7 +9704,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893374</v>
+        <v>129893388</v>
       </c>
       <c r="B92" t="n">
         <v>79095</v>
@@ -9742,10 +9739,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447470</v>
+        <v>447312</v>
       </c>
       <c r="R92" t="n">
-        <v>6805005</v>
+        <v>6804705</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9778,11 +9775,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9809,10 +9801,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893389</v>
+        <v>129893321</v>
       </c>
       <c r="B93" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9820,34 +9812,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447326</v>
+        <v>447539</v>
       </c>
       <c r="R93" t="n">
-        <v>6804648</v>
+        <v>6804888</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129893911</v>
+        <v>129894015</v>
       </c>
       <c r="B2" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447312</v>
+        <v>447460</v>
       </c>
       <c r="R2" t="n">
-        <v>6804764</v>
+        <v>6804726</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894015</v>
+        <v>129893911</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447460</v>
+        <v>447312</v>
       </c>
       <c r="R3" t="n">
-        <v>6804726</v>
+        <v>6804764</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893997</v>
+        <v>129893947</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>78938</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447419</v>
+        <v>447580</v>
       </c>
       <c r="R4" t="n">
-        <v>6804565</v>
+        <v>6804504</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893947</v>
+        <v>129893997</v>
       </c>
       <c r="B5" t="n">
-        <v>78853</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447580</v>
+        <v>447419</v>
       </c>
       <c r="R5" t="n">
-        <v>6804504</v>
+        <v>6804565</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>129893993</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129894004</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129894008</v>
+        <v>129894014</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447529</v>
+        <v>447482</v>
       </c>
       <c r="R8" t="n">
-        <v>6804634</v>
+        <v>6804743</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129894014</v>
+        <v>129894008</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447482</v>
+        <v>447529</v>
       </c>
       <c r="R9" t="n">
-        <v>6804743</v>
+        <v>6804634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
         <v>129893994</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>129894003</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>129894022</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>129893941</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>129893915</v>
       </c>
       <c r="B14" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>129893901</v>
       </c>
       <c r="B15" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>129893909</v>
       </c>
       <c r="B16" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>129893930</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2256,45 +2256,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893904</v>
+        <v>129893922</v>
       </c>
       <c r="B18" t="n">
-        <v>79714</v>
+        <v>57016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447491</v>
+        <v>447455</v>
       </c>
       <c r="R18" t="n">
-        <v>6804595</v>
+        <v>6804619</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2353,53 +2361,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893922</v>
+        <v>129893904</v>
       </c>
       <c r="B19" t="n">
-        <v>56931</v>
+        <v>79799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447455</v>
+        <v>447491</v>
       </c>
       <c r="R19" t="n">
-        <v>6804619</v>
+        <v>6804595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,7 +2461,7 @@
         <v>129894002</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>129893996</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,45 +2652,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894048</v>
+        <v>129893958</v>
       </c>
       <c r="B22" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447408</v>
+        <v>447566</v>
       </c>
       <c r="R22" t="n">
-        <v>6804651</v>
+        <v>6804650</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,6 +2740,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2749,10 +2759,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894010</v>
+        <v>129893907</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2760,21 +2770,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2784,10 +2794,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447599</v>
+        <v>447541</v>
       </c>
       <c r="R23" t="n">
-        <v>6804708</v>
+        <v>6804663</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,10 +2856,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893907</v>
+        <v>129894048</v>
       </c>
       <c r="B24" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2857,21 +2867,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2881,10 +2891,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447541</v>
+        <v>447408</v>
       </c>
       <c r="R24" t="n">
-        <v>6804663</v>
+        <v>6804651</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2943,54 +2953,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129893958</v>
+        <v>129894010</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447566</v>
+        <v>447599</v>
       </c>
       <c r="R25" t="n">
-        <v>6804650</v>
+        <v>6804708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3031,7 +3032,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>129893905</v>
       </c>
       <c r="B26" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>129893928</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894016</v>
+        <v>129893903</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3370,21 +3370,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447444</v>
+        <v>447486</v>
       </c>
       <c r="R29" t="n">
-        <v>6804723</v>
+        <v>6804619</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3456,10 +3456,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894009</v>
+        <v>129893902</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3467,21 +3467,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3491,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447538</v>
+        <v>447430</v>
       </c>
       <c r="R30" t="n">
-        <v>6804692</v>
+        <v>6804548</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3527,11 +3527,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3558,10 +3553,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894011</v>
+        <v>129894016</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3593,10 +3588,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447589</v>
+        <v>447444</v>
       </c>
       <c r="R31" t="n">
-        <v>6804744</v>
+        <v>6804723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3629,11 +3624,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3660,45 +3650,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129893903</v>
+        <v>129893957</v>
       </c>
       <c r="B32" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447486</v>
+        <v>447418</v>
       </c>
       <c r="R32" t="n">
-        <v>6804619</v>
+        <v>6804561</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3739,6 +3738,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3757,10 +3757,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893902</v>
+        <v>129894009</v>
       </c>
       <c r="B33" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3768,21 +3768,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447430</v>
+        <v>447538</v>
       </c>
       <c r="R33" t="n">
-        <v>6804548</v>
+        <v>6804692</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3828,6 +3828,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,54 +3859,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893957</v>
+        <v>129894011</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447418</v>
+        <v>447589</v>
       </c>
       <c r="R34" t="n">
-        <v>6804561</v>
+        <v>6804744</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3936,13 +3932,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3961,10 +3961,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129893908</v>
+        <v>129893916</v>
       </c>
       <c r="B35" t="n">
-        <v>79714</v>
+        <v>79770</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3972,21 +3972,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3996,10 +3996,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447543</v>
+        <v>447402</v>
       </c>
       <c r="R35" t="n">
-        <v>6804684</v>
+        <v>6804565</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4058,10 +4058,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129893929</v>
+        <v>129893908</v>
       </c>
       <c r="B36" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4069,42 +4069,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447594</v>
+        <v>447543</v>
       </c>
       <c r="R36" t="n">
-        <v>6804744</v>
+        <v>6804684</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4163,10 +4155,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129893916</v>
+        <v>129893929</v>
       </c>
       <c r="B37" t="n">
-        <v>79685</v>
+        <v>57823</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4174,34 +4166,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447402</v>
+        <v>447594</v>
       </c>
       <c r="R37" t="n">
-        <v>6804565</v>
+        <v>6804744</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4263,7 +4263,7 @@
         <v>129894005</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4366,45 +4366,54 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894001</v>
+        <v>129893962</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447491</v>
+        <v>447552</v>
       </c>
       <c r="R39" t="n">
-        <v>6804629</v>
+        <v>6804720</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,6 +4454,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4466,7 +4476,7 @@
         <v>129893927</v>
       </c>
       <c r="B40" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4568,54 +4578,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893962</v>
+        <v>129894001</v>
       </c>
       <c r="B41" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447552</v>
+        <v>447491</v>
       </c>
       <c r="R41" t="n">
-        <v>6804720</v>
+        <v>6804629</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4656,7 +4657,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4675,45 +4675,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129893998</v>
+        <v>129893959</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447424</v>
+        <v>447540</v>
       </c>
       <c r="R42" t="n">
-        <v>6804554</v>
+        <v>6804664</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4754,6 +4763,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4772,10 +4782,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894007</v>
+        <v>129893998</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4807,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447533</v>
+        <v>447424</v>
       </c>
       <c r="R43" t="n">
-        <v>6804620</v>
+        <v>6804554</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4843,11 +4853,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4874,10 +4879,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894000</v>
+        <v>129893966</v>
       </c>
       <c r="B44" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4885,21 +4890,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4909,10 +4914,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447442</v>
+        <v>447483</v>
       </c>
       <c r="R44" t="n">
-        <v>6804551</v>
+        <v>6804616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4945,11 +4950,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 30m.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4976,10 +4976,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894020</v>
+        <v>129894007</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5011,10 +5011,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447306</v>
+        <v>447533</v>
       </c>
       <c r="R45" t="n">
-        <v>6804757</v>
+        <v>6804620</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5047,6 +5047,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 50 m.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5073,54 +5078,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893959</v>
+        <v>129894000</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447540</v>
+        <v>447442</v>
       </c>
       <c r="R46" t="n">
-        <v>6804664</v>
+        <v>6804551</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5155,13 +5151,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5180,10 +5180,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893966</v>
+        <v>129894020</v>
       </c>
       <c r="B47" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5191,21 +5191,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5215,10 +5215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447483</v>
+        <v>447306</v>
       </c>
       <c r="R47" t="n">
-        <v>6804616</v>
+        <v>6804757</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5280,7 +5280,7 @@
         <v>129893999</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>129893906</v>
       </c>
       <c r="B49" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>129893931</v>
       </c>
       <c r="B50" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5576,54 +5576,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893961</v>
+        <v>129894021</v>
       </c>
       <c r="B51" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447559</v>
+        <v>447330</v>
       </c>
       <c r="R51" t="n">
-        <v>6804728</v>
+        <v>6804680</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5658,13 +5649,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5683,10 +5678,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894021</v>
+        <v>129894006</v>
       </c>
       <c r="B52" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5718,10 +5713,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447330</v>
+        <v>447575</v>
       </c>
       <c r="R52" t="n">
-        <v>6804680</v>
+        <v>6804539</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5754,11 +5749,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5785,45 +5775,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129894006</v>
+        <v>129893961</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447575</v>
+        <v>447559</v>
       </c>
       <c r="R53" t="n">
-        <v>6804539</v>
+        <v>6804728</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5864,6 +5863,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>129893995</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5979,10 +5979,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129893992</v>
+        <v>129893917</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>79770</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447390</v>
+        <v>447580</v>
       </c>
       <c r="R55" t="n">
-        <v>6804568</v>
+        <v>6804527</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6050,11 +6050,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6081,10 +6076,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129893917</v>
+        <v>129893992</v>
       </c>
       <c r="B56" t="n">
-        <v>79685</v>
+        <v>79180</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6092,21 +6087,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6116,10 +6111,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447580</v>
+        <v>447390</v>
       </c>
       <c r="R56" t="n">
-        <v>6804527</v>
+        <v>6804568</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6152,6 +6147,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6181,7 +6181,7 @@
         <v>129894012</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         <v>129894013</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>129893910</v>
       </c>
       <c r="B59" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6469,40 +6469,41 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893320</v>
+        <v>129893335</v>
       </c>
       <c r="B60" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -6512,10 +6513,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447517</v>
+        <v>447503</v>
       </c>
       <c r="R60" t="n">
-        <v>6804957</v>
+        <v>6804998</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6556,6 +6557,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6574,41 +6576,40 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893335</v>
+        <v>129893320</v>
       </c>
       <c r="B61" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -6618,10 +6619,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447503</v>
+        <v>447517</v>
       </c>
       <c r="R61" t="n">
-        <v>6804998</v>
+        <v>6804957</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6662,7 +6663,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6684,7 +6684,7 @@
         <v>129893327</v>
       </c>
       <c r="B62" t="n">
-        <v>80201</v>
+        <v>80286</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>129893319</v>
       </c>
       <c r="B63" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>129893371</v>
       </c>
       <c r="B64" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>129893373</v>
       </c>
       <c r="B65" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7087,10 +7087,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893369</v>
+        <v>129893341</v>
       </c>
       <c r="B66" t="n">
-        <v>79095</v>
+        <v>80285</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7098,34 +7098,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447459</v>
+        <v>447580</v>
       </c>
       <c r="R66" t="n">
-        <v>6804815</v>
+        <v>6804735</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7160,12 +7163,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7184,10 +7193,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893341</v>
+        <v>129893318</v>
       </c>
       <c r="B67" t="n">
-        <v>80200</v>
+        <v>57823</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7195,26 +7204,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7222,10 +7236,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447580</v>
+        <v>447384</v>
       </c>
       <c r="R67" t="n">
-        <v>6804735</v>
+        <v>6805028</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7260,18 +7274,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7290,10 +7298,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893318</v>
+        <v>129893369</v>
       </c>
       <c r="B68" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7301,42 +7309,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447384</v>
+        <v>447459</v>
       </c>
       <c r="R68" t="n">
-        <v>6805028</v>
+        <v>6804815</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7398,7 +7398,7 @@
         <v>129893317</v>
       </c>
       <c r="B69" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7500,45 +7500,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129893390</v>
+        <v>129893337</v>
       </c>
       <c r="B70" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447328</v>
+        <v>447532</v>
       </c>
       <c r="R70" t="n">
-        <v>6804646</v>
+        <v>6804904</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7579,6 +7588,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7597,54 +7607,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129893337</v>
+        <v>129893390</v>
       </c>
       <c r="B71" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447532</v>
+        <v>447328</v>
       </c>
       <c r="R71" t="n">
-        <v>6804904</v>
+        <v>6804646</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7685,7 +7686,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7707,7 +7707,7 @@
         <v>129893380</v>
       </c>
       <c r="B72" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>129893386</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>129893372</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>129893387</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>129893377</v>
       </c>
       <c r="B76" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>129893379</v>
       </c>
       <c r="B77" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>129893292</v>
       </c>
       <c r="B79" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8505,45 +8505,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893376</v>
+        <v>129893340</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447576</v>
+        <v>447459</v>
       </c>
       <c r="R80" t="n">
-        <v>6804770</v>
+        <v>6804731</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8584,6 +8593,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8602,54 +8612,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893340</v>
+        <v>129893376</v>
       </c>
       <c r="B81" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447459</v>
+        <v>447576</v>
       </c>
       <c r="R81" t="n">
-        <v>6804731</v>
+        <v>6804770</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8690,7 +8691,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>129893370</v>
       </c>
       <c r="B82" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>129893375</v>
       </c>
       <c r="B83" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>129893378</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9010,10 +9010,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893381</v>
+        <v>129893293</v>
       </c>
       <c r="B85" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9021,21 +9021,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447451</v>
+        <v>447420</v>
       </c>
       <c r="R85" t="n">
-        <v>6804727</v>
+        <v>6804795</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9107,10 +9107,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893293</v>
+        <v>129893381</v>
       </c>
       <c r="B86" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9118,21 +9118,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9142,10 +9142,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447420</v>
+        <v>447451</v>
       </c>
       <c r="R86" t="n">
-        <v>6804795</v>
+        <v>6804727</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9204,10 +9204,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129893382</v>
+        <v>129893294</v>
       </c>
       <c r="B87" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9215,21 +9215,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447448</v>
+        <v>447422</v>
       </c>
       <c r="R87" t="n">
-        <v>6804705</v>
+        <v>6805021</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9408,10 +9408,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893294</v>
+        <v>129893382</v>
       </c>
       <c r="B89" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9419,21 +9419,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9443,10 +9443,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447422</v>
+        <v>447448</v>
       </c>
       <c r="R89" t="n">
-        <v>6805021</v>
+        <v>6804705</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9508,7 +9508,7 @@
         <v>129893374</v>
       </c>
       <c r="B90" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>129893389</v>
       </c>
       <c r="B91" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>129893388</v>
       </c>
       <c r="B92" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>129893321</v>
       </c>
       <c r="B93" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9904,6 +9904,2596 @@
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>132748966</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>447592</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6804556</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>132748965</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>447600</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6804545</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>132748969</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>447606</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6804603</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>132748978</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>447673</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6804560</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>132748960</v>
+      </c>
+      <c r="B98" t="n">
+        <v>78993</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>353</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>447587</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6804616</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>132748972</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>447616</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6804588</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>132748986</v>
+      </c>
+      <c r="B100" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>447663</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6804623</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>132748976</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>447660</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6804565</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>132748958</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>447602</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6804649</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>132748962</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>447586</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6804596</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>132748952</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>447598</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6804708</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>132748964</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>447597</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6804539</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>132748961</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>447585</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6804598</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>132748959</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>447584</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6804624</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>132748979</v>
+      </c>
+      <c r="B108" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>447677</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6804549</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>132748967</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>447595</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6804550</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>132748963</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>447587</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6804575</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>132748983</v>
+      </c>
+      <c r="B111" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>447651</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6804611</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>132748970</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>447609</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6804599</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>132748975</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>447624</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6804577</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>132748980</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>447679</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6804579</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>132748971</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79359</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>185</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>447611</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6804594</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>132748968</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>447606</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6804603</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>132748974</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>447619</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6804597</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -11747,32 +11747,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132748983</v>
+        <v>132748970</v>
       </c>
       <c r="B111" t="n">
-        <v>91909</v>
+        <v>79413</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>6450</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447651</v>
+        <v>447609</v>
       </c>
       <c r="R111" t="n">
-        <v>6804611</v>
+        <v>6804599</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11854,32 +11854,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132748970</v>
+        <v>132748975</v>
       </c>
       <c r="B112" t="n">
-        <v>79413</v>
+        <v>79327</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11889,10 +11889,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447609</v>
+        <v>447624</v>
       </c>
       <c r="R112" t="n">
-        <v>6804599</v>
+        <v>6804577</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11961,10 +11961,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748975</v>
+        <v>132748983</v>
       </c>
       <c r="B113" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11972,21 +11972,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447624</v>
+        <v>447651</v>
       </c>
       <c r="R113" t="n">
-        <v>6804577</v>
+        <v>6804611</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD113" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -10120,32 +10120,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132748969</v>
+        <v>132748978</v>
       </c>
       <c r="B96" t="n">
-        <v>79413</v>
+        <v>79327</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447606</v>
+        <v>447673</v>
       </c>
       <c r="R96" t="n">
-        <v>6804603</v>
+        <v>6804560</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10227,32 +10227,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132748978</v>
+        <v>132748969</v>
       </c>
       <c r="B97" t="n">
-        <v>79327</v>
+        <v>79413</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10262,10 +10262,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447673</v>
+        <v>447606</v>
       </c>
       <c r="R97" t="n">
-        <v>6804560</v>
+        <v>6804603</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11640,10 +11640,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132748963</v>
+        <v>132748983</v>
       </c>
       <c r="B110" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447587</v>
+        <v>447651</v>
       </c>
       <c r="R110" t="n">
-        <v>6804575</v>
+        <v>6804611</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11961,10 +11961,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748983</v>
+        <v>132748963</v>
       </c>
       <c r="B113" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11972,21 +11972,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447651</v>
+        <v>447587</v>
       </c>
       <c r="R113" t="n">
-        <v>6804611</v>
+        <v>6804575</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD113" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -10120,32 +10120,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132748978</v>
+        <v>132748969</v>
       </c>
       <c r="B96" t="n">
-        <v>79327</v>
+        <v>79413</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10155,10 +10155,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447673</v>
+        <v>447606</v>
       </c>
       <c r="R96" t="n">
-        <v>6804560</v>
+        <v>6804603</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10190,7 +10190,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10227,32 +10227,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>132748969</v>
+        <v>132748978</v>
       </c>
       <c r="B97" t="n">
-        <v>79413</v>
+        <v>79327</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10262,10 +10262,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447606</v>
+        <v>447673</v>
       </c>
       <c r="R97" t="n">
-        <v>6804603</v>
+        <v>6804560</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11747,32 +11747,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132748970</v>
+        <v>132748975</v>
       </c>
       <c r="B111" t="n">
-        <v>79413</v>
+        <v>79327</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447609</v>
+        <v>447624</v>
       </c>
       <c r="R111" t="n">
-        <v>6804599</v>
+        <v>6804577</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11854,7 +11854,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132748975</v>
+        <v>132748963</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -11889,10 +11889,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447624</v>
+        <v>447587</v>
       </c>
       <c r="R112" t="n">
-        <v>6804577</v>
+        <v>6804575</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11961,32 +11961,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748963</v>
+        <v>132748970</v>
       </c>
       <c r="B113" t="n">
-        <v>79327</v>
+        <v>79413</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447587</v>
+        <v>447609</v>
       </c>
       <c r="R113" t="n">
-        <v>6804575</v>
+        <v>6804599</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD113" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY117"/>
+  <dimension ref="A1:AY123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10548,10 +10548,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132748986</v>
+        <v>132748976</v>
       </c>
       <c r="B100" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10559,21 +10559,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10583,10 +10583,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447663</v>
+        <v>447660</v>
       </c>
       <c r="R100" t="n">
-        <v>6804623</v>
+        <v>6804565</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10655,10 +10655,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132748976</v>
+        <v>132748986</v>
       </c>
       <c r="B101" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10666,21 +10666,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447660</v>
+        <v>447663</v>
       </c>
       <c r="R101" t="n">
-        <v>6804565</v>
+        <v>6804623</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12494,6 +12494,588 @@
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>132844422</v>
+      </c>
+      <c r="B118" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>447604</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6804547</v>
+      </c>
+      <c r="S118" t="n">
+        <v>25</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>132844417</v>
+      </c>
+      <c r="B119" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>447601</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6804599</v>
+      </c>
+      <c r="S119" t="n">
+        <v>25</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>132844419</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>447589</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6804585</v>
+      </c>
+      <c r="S120" t="n">
+        <v>25</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>132844424</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>447592</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6804573</v>
+      </c>
+      <c r="S121" t="n">
+        <v>25</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>132844420</v>
+      </c>
+      <c r="B122" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>447588</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6804577</v>
+      </c>
+      <c r="S122" t="n">
+        <v>25</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>132844425</v>
+      </c>
+      <c r="B123" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Jöllen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>447607</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6804594</v>
+      </c>
+      <c r="S123" t="n">
+        <v>25</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -9909,7 +9909,7 @@
         <v>132748966</v>
       </c>
       <c r="B94" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>132748965</v>
       </c>
       <c r="B95" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>132748969</v>
       </c>
       <c r="B96" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>132748978</v>
       </c>
       <c r="B97" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>132748960</v>
       </c>
       <c r="B98" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>132748972</v>
       </c>
       <c r="B99" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>132748976</v>
       </c>
       <c r="B100" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>132748986</v>
       </c>
       <c r="B101" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>132748958</v>
       </c>
       <c r="B102" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>132748962</v>
       </c>
       <c r="B103" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>132748952</v>
       </c>
       <c r="B104" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>132748964</v>
       </c>
       <c r="B105" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>132748961</v>
       </c>
       <c r="B106" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11314,45 +11314,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132748959</v>
+        <v>132748979</v>
       </c>
       <c r="B107" t="n">
-        <v>79327</v>
+        <v>5179</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447584</v>
+        <v>447677</v>
       </c>
       <c r="R107" t="n">
-        <v>6804624</v>
+        <v>6804549</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11384,7 +11389,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11394,7 +11399,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11421,50 +11426,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132748979</v>
+        <v>132748959</v>
       </c>
       <c r="B108" t="n">
-        <v>5179</v>
+        <v>79328</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447677</v>
+        <v>447584</v>
       </c>
       <c r="R108" t="n">
-        <v>6804549</v>
+        <v>6804624</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11536,7 +11536,7 @@
         <v>132748967</v>
       </c>
       <c r="B109" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11640,10 +11640,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132748983</v>
+        <v>132748975</v>
       </c>
       <c r="B110" t="n">
-        <v>91909</v>
+        <v>79328</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447651</v>
+        <v>447624</v>
       </c>
       <c r="R110" t="n">
-        <v>6804611</v>
+        <v>6804577</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11747,10 +11747,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132748975</v>
+        <v>132748963</v>
       </c>
       <c r="B111" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447624</v>
+        <v>447587</v>
       </c>
       <c r="R111" t="n">
-        <v>6804577</v>
+        <v>6804575</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11854,32 +11854,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132748963</v>
+        <v>132748970</v>
       </c>
       <c r="B112" t="n">
-        <v>79327</v>
+        <v>79414</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11889,10 +11889,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447587</v>
+        <v>447609</v>
       </c>
       <c r="R112" t="n">
-        <v>6804575</v>
+        <v>6804599</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11961,32 +11961,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748970</v>
+        <v>132748983</v>
       </c>
       <c r="B113" t="n">
-        <v>79413</v>
+        <v>91910</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6450</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447609</v>
+        <v>447651</v>
       </c>
       <c r="R113" t="n">
-        <v>6804599</v>
+        <v>6804611</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12071,7 +12071,7 @@
         <v>132748980</v>
       </c>
       <c r="B114" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>132748971</v>
       </c>
       <c r="B115" t="n">
-        <v>79359</v>
+        <v>79360</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>132748968</v>
       </c>
       <c r="B116" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>132748974</v>
       </c>
       <c r="B117" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>132844422</v>
       </c>
       <c r="B118" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>132844417</v>
       </c>
       <c r="B119" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>132844419</v>
       </c>
       <c r="B120" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>132844424</v>
       </c>
       <c r="B121" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>132844420</v>
       </c>
       <c r="B122" t="n">
-        <v>79413</v>
+        <v>79414</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>132844425</v>
       </c>
       <c r="B123" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -10548,10 +10548,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132748976</v>
+        <v>132748986</v>
       </c>
       <c r="B100" t="n">
-        <v>79328</v>
+        <v>91912</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10559,21 +10559,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10583,10 +10583,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447660</v>
+        <v>447663</v>
       </c>
       <c r="R100" t="n">
-        <v>6804565</v>
+        <v>6804623</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10655,10 +10655,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132748986</v>
+        <v>132748976</v>
       </c>
       <c r="B101" t="n">
-        <v>91910</v>
+        <v>79328</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10666,21 +10666,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447663</v>
+        <v>447660</v>
       </c>
       <c r="R101" t="n">
-        <v>6804623</v>
+        <v>6804565</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11314,50 +11314,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132748979</v>
+        <v>132748959</v>
       </c>
       <c r="B107" t="n">
-        <v>5179</v>
+        <v>79328</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447677</v>
+        <v>447584</v>
       </c>
       <c r="R107" t="n">
-        <v>6804549</v>
+        <v>6804624</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11389,7 +11384,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11399,7 +11394,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11426,45 +11421,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132748959</v>
+        <v>132748979</v>
       </c>
       <c r="B108" t="n">
-        <v>79328</v>
+        <v>5179</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447584</v>
+        <v>447677</v>
       </c>
       <c r="R108" t="n">
-        <v>6804624</v>
+        <v>6804549</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11640,10 +11640,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132748975</v>
+        <v>132748983</v>
       </c>
       <c r="B110" t="n">
-        <v>79328</v>
+        <v>91912</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447624</v>
+        <v>447651</v>
       </c>
       <c r="R110" t="n">
-        <v>6804577</v>
+        <v>6804611</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11747,7 +11747,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132748963</v>
+        <v>132748975</v>
       </c>
       <c r="B111" t="n">
         <v>79328</v>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447587</v>
+        <v>447624</v>
       </c>
       <c r="R111" t="n">
-        <v>6804575</v>
+        <v>6804577</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11854,32 +11854,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132748970</v>
+        <v>132748963</v>
       </c>
       <c r="B112" t="n">
-        <v>79414</v>
+        <v>79328</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11889,10 +11889,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447609</v>
+        <v>447587</v>
       </c>
       <c r="R112" t="n">
-        <v>6804599</v>
+        <v>6804575</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11961,32 +11961,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748983</v>
+        <v>132748970</v>
       </c>
       <c r="B113" t="n">
-        <v>91910</v>
+        <v>79414</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6450</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447651</v>
+        <v>447609</v>
       </c>
       <c r="R113" t="n">
-        <v>6804611</v>
+        <v>6804599</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12071,7 +12071,7 @@
         <v>132748980</v>
       </c>
       <c r="B114" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>132844417</v>
       </c>
       <c r="B119" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -9909,7 +9909,7 @@
         <v>132748966</v>
       </c>
       <c r="B94" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>132748965</v>
       </c>
       <c r="B95" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10123,7 +10123,7 @@
         <v>132748969</v>
       </c>
       <c r="B96" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>132748978</v>
       </c>
       <c r="B97" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         <v>132748960</v>
       </c>
       <c r="B98" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>132748972</v>
       </c>
       <c r="B99" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>132748986</v>
       </c>
       <c r="B100" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>132748976</v>
       </c>
       <c r="B101" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>132748958</v>
       </c>
       <c r="B102" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10872,7 +10872,7 @@
         <v>132748962</v>
       </c>
       <c r="B103" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>132748952</v>
       </c>
       <c r="B104" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>132748964</v>
       </c>
       <c r="B105" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>132748961</v>
       </c>
       <c r="B106" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>132748959</v>
       </c>
       <c r="B107" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>132748967</v>
       </c>
       <c r="B109" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11640,10 +11640,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132748983</v>
+        <v>132748963</v>
       </c>
       <c r="B110" t="n">
-        <v>91912</v>
+        <v>79329</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447651</v>
+        <v>447587</v>
       </c>
       <c r="R110" t="n">
-        <v>6804611</v>
+        <v>6804575</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11747,32 +11747,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132748975</v>
+        <v>132748970</v>
       </c>
       <c r="B111" t="n">
-        <v>79328</v>
+        <v>79415</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447624</v>
+        <v>447609</v>
       </c>
       <c r="R111" t="n">
-        <v>6804577</v>
+        <v>6804599</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11854,10 +11854,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132748963</v>
+        <v>132748975</v>
       </c>
       <c r="B112" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11889,10 +11889,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447587</v>
+        <v>447624</v>
       </c>
       <c r="R112" t="n">
-        <v>6804575</v>
+        <v>6804577</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11961,32 +11961,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748970</v>
+        <v>132748983</v>
       </c>
       <c r="B113" t="n">
-        <v>79414</v>
+        <v>91913</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6450</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447609</v>
+        <v>447651</v>
       </c>
       <c r="R113" t="n">
-        <v>6804599</v>
+        <v>6804611</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12071,7 +12071,7 @@
         <v>132748980</v>
       </c>
       <c r="B114" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>132748971</v>
       </c>
       <c r="B115" t="n">
-        <v>79360</v>
+        <v>79361</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>132748968</v>
       </c>
       <c r="B116" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>132748974</v>
       </c>
       <c r="B117" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>132844422</v>
       </c>
       <c r="B118" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12596,7 +12596,7 @@
         <v>132844417</v>
       </c>
       <c r="B119" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>132844419</v>
       </c>
       <c r="B120" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>132844424</v>
       </c>
       <c r="B121" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>132844420</v>
       </c>
       <c r="B122" t="n">
-        <v>79414</v>
+        <v>79415</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>132844425</v>
       </c>
       <c r="B123" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -10548,10 +10548,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132748986</v>
+        <v>132748976</v>
       </c>
       <c r="B100" t="n">
-        <v>91913</v>
+        <v>79329</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10559,21 +10559,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10583,10 +10583,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447663</v>
+        <v>447660</v>
       </c>
       <c r="R100" t="n">
-        <v>6804623</v>
+        <v>6804565</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10655,10 +10655,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132748976</v>
+        <v>132748986</v>
       </c>
       <c r="B101" t="n">
-        <v>79329</v>
+        <v>91913</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10666,21 +10666,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447660</v>
+        <v>447663</v>
       </c>
       <c r="R101" t="n">
-        <v>6804565</v>
+        <v>6804623</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11314,45 +11314,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132748959</v>
+        <v>132748979</v>
       </c>
       <c r="B107" t="n">
-        <v>79329</v>
+        <v>5179</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447584</v>
+        <v>447677</v>
       </c>
       <c r="R107" t="n">
-        <v>6804624</v>
+        <v>6804549</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11384,7 +11389,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11394,7 +11399,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11421,50 +11426,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132748979</v>
+        <v>132748959</v>
       </c>
       <c r="B108" t="n">
-        <v>5179</v>
+        <v>79329</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447677</v>
+        <v>447584</v>
       </c>
       <c r="R108" t="n">
-        <v>6804549</v>
+        <v>6804624</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD108" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -10548,10 +10548,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>132748976</v>
+        <v>132748986</v>
       </c>
       <c r="B100" t="n">
-        <v>79329</v>
+        <v>91913</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10559,21 +10559,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10583,10 +10583,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447660</v>
+        <v>447663</v>
       </c>
       <c r="R100" t="n">
-        <v>6804565</v>
+        <v>6804623</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10618,7 +10618,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10655,10 +10655,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>132748986</v>
+        <v>132748976</v>
       </c>
       <c r="B101" t="n">
-        <v>91913</v>
+        <v>79329</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10666,21 +10666,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10690,10 +10690,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447663</v>
+        <v>447660</v>
       </c>
       <c r="R101" t="n">
-        <v>6804623</v>
+        <v>6804565</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11314,50 +11314,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132748979</v>
+        <v>132748959</v>
       </c>
       <c r="B107" t="n">
-        <v>5179</v>
+        <v>79329</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447677</v>
+        <v>447584</v>
       </c>
       <c r="R107" t="n">
-        <v>6804549</v>
+        <v>6804624</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11389,7 +11384,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11399,7 +11394,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11426,45 +11421,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132748959</v>
+        <v>132748979</v>
       </c>
       <c r="B108" t="n">
-        <v>79329</v>
+        <v>5179</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447584</v>
+        <v>447677</v>
       </c>
       <c r="R108" t="n">
-        <v>6804624</v>
+        <v>6804549</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11640,10 +11640,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132748963</v>
+        <v>132748983</v>
       </c>
       <c r="B110" t="n">
-        <v>79329</v>
+        <v>91913</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447587</v>
+        <v>447651</v>
       </c>
       <c r="R110" t="n">
-        <v>6804575</v>
+        <v>6804611</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11747,32 +11747,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132748970</v>
+        <v>132748963</v>
       </c>
       <c r="B111" t="n">
-        <v>79415</v>
+        <v>79329</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447609</v>
+        <v>447587</v>
       </c>
       <c r="R111" t="n">
-        <v>6804599</v>
+        <v>6804575</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11854,32 +11854,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132748975</v>
+        <v>132748970</v>
       </c>
       <c r="B112" t="n">
-        <v>79329</v>
+        <v>79415</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11889,10 +11889,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447624</v>
+        <v>447609</v>
       </c>
       <c r="R112" t="n">
-        <v>6804577</v>
+        <v>6804599</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11961,10 +11961,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748983</v>
+        <v>132748975</v>
       </c>
       <c r="B113" t="n">
-        <v>91913</v>
+        <v>79329</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11972,21 +11972,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447651</v>
+        <v>447624</v>
       </c>
       <c r="R113" t="n">
-        <v>6804611</v>
+        <v>6804577</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12282,32 +12282,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132748968</v>
+        <v>132748974</v>
       </c>
       <c r="B116" t="n">
-        <v>79329</v>
+        <v>79415</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447606</v>
+        <v>447619</v>
       </c>
       <c r="R116" t="n">
-        <v>6804603</v>
+        <v>6804597</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12389,32 +12389,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132748974</v>
+        <v>132748968</v>
       </c>
       <c r="B117" t="n">
-        <v>79415</v>
+        <v>79329</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12424,10 +12424,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447619</v>
+        <v>447606</v>
       </c>
       <c r="R117" t="n">
-        <v>6804597</v>
+        <v>6804603</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -12282,32 +12282,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132748974</v>
+        <v>132748968</v>
       </c>
       <c r="B116" t="n">
-        <v>79415</v>
+        <v>79329</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447619</v>
+        <v>447606</v>
       </c>
       <c r="R116" t="n">
-        <v>6804597</v>
+        <v>6804603</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12389,32 +12389,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132748968</v>
+        <v>132748974</v>
       </c>
       <c r="B117" t="n">
-        <v>79329</v>
+        <v>79415</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12424,10 +12424,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447606</v>
+        <v>447619</v>
       </c>
       <c r="R117" t="n">
-        <v>6804603</v>
+        <v>6804597</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -12282,32 +12282,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132748968</v>
+        <v>132748974</v>
       </c>
       <c r="B116" t="n">
-        <v>79329</v>
+        <v>79415</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447606</v>
+        <v>447619</v>
       </c>
       <c r="R116" t="n">
-        <v>6804603</v>
+        <v>6804597</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12389,32 +12389,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132748974</v>
+        <v>132748968</v>
       </c>
       <c r="B117" t="n">
-        <v>79415</v>
+        <v>79329</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12424,10 +12424,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447619</v>
+        <v>447606</v>
       </c>
       <c r="R117" t="n">
-        <v>6804597</v>
+        <v>6804603</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -11314,50 +11314,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132748979</v>
+        <v>132748959</v>
       </c>
       <c r="B107" t="n">
-        <v>5179</v>
+        <v>79333</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447677</v>
+        <v>447584</v>
       </c>
       <c r="R107" t="n">
-        <v>6804549</v>
+        <v>6804624</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11389,7 +11384,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11399,7 +11394,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11426,45 +11421,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132748959</v>
+        <v>132748979</v>
       </c>
       <c r="B108" t="n">
-        <v>79333</v>
+        <v>5179</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447584</v>
+        <v>447677</v>
       </c>
       <c r="R108" t="n">
-        <v>6804624</v>
+        <v>6804549</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11640,10 +11640,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132748983</v>
+        <v>132748963</v>
       </c>
       <c r="B110" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447651</v>
+        <v>447587</v>
       </c>
       <c r="R110" t="n">
-        <v>6804611</v>
+        <v>6804575</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11747,32 +11747,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132748963</v>
+        <v>132748970</v>
       </c>
       <c r="B111" t="n">
-        <v>79333</v>
+        <v>79419</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447587</v>
+        <v>447609</v>
       </c>
       <c r="R111" t="n">
-        <v>6804575</v>
+        <v>6804599</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11961,32 +11961,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748970</v>
+        <v>132748983</v>
       </c>
       <c r="B113" t="n">
-        <v>79419</v>
+        <v>91918</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6450</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447609</v>
+        <v>447651</v>
       </c>
       <c r="R113" t="n">
-        <v>6804599</v>
+        <v>6804611</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD113" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -10762,32 +10762,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132748958</v>
+        <v>132748962</v>
       </c>
       <c r="B102" t="n">
-        <v>79333</v>
+        <v>79419</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447602</v>
+        <v>447586</v>
       </c>
       <c r="R102" t="n">
-        <v>6804649</v>
+        <v>6804596</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10869,32 +10869,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132748962</v>
+        <v>132748958</v>
       </c>
       <c r="B103" t="n">
-        <v>79419</v>
+        <v>79333</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447586</v>
+        <v>447602</v>
       </c>
       <c r="R103" t="n">
-        <v>6804596</v>
+        <v>6804649</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11088,45 +11088,56 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132748964</v>
+        <v>132748961</v>
       </c>
       <c r="B105" t="n">
-        <v>79333</v>
+        <v>79419</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447597</v>
+        <v>447585</v>
       </c>
       <c r="R105" t="n">
-        <v>6804539</v>
+        <v>6804598</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11158,7 +11169,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11168,7 +11179,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11177,6 +11188,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11195,56 +11207,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132748961</v>
+        <v>132748964</v>
       </c>
       <c r="B106" t="n">
-        <v>79419</v>
+        <v>79333</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447585</v>
+        <v>447597</v>
       </c>
       <c r="R106" t="n">
-        <v>6804598</v>
+        <v>6804539</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11276,7 +11277,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11286,7 +11287,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11295,7 +11296,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11640,10 +11640,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132748963</v>
+        <v>132748983</v>
       </c>
       <c r="B110" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447587</v>
+        <v>447651</v>
       </c>
       <c r="R110" t="n">
-        <v>6804575</v>
+        <v>6804611</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11961,10 +11961,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748983</v>
+        <v>132748963</v>
       </c>
       <c r="B113" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11972,21 +11972,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447651</v>
+        <v>447587</v>
       </c>
       <c r="R113" t="n">
-        <v>6804611</v>
+        <v>6804575</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12282,32 +12282,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132748968</v>
+        <v>132748974</v>
       </c>
       <c r="B116" t="n">
-        <v>79333</v>
+        <v>79419</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447606</v>
+        <v>447619</v>
       </c>
       <c r="R116" t="n">
-        <v>6804603</v>
+        <v>6804597</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12389,32 +12389,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132748974</v>
+        <v>132748968</v>
       </c>
       <c r="B117" t="n">
-        <v>79419</v>
+        <v>79333</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12424,10 +12424,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447619</v>
+        <v>447606</v>
       </c>
       <c r="R117" t="n">
-        <v>6804597</v>
+        <v>6804603</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -11088,56 +11088,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>132748961</v>
+        <v>132748964</v>
       </c>
       <c r="B105" t="n">
-        <v>79419</v>
+        <v>79333</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447585</v>
+        <v>447597</v>
       </c>
       <c r="R105" t="n">
-        <v>6804598</v>
+        <v>6804539</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11169,7 +11158,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11179,7 +11168,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11188,7 +11177,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11207,45 +11195,56 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>132748964</v>
+        <v>132748961</v>
       </c>
       <c r="B106" t="n">
-        <v>79333</v>
+        <v>79419</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447597</v>
+        <v>447585</v>
       </c>
       <c r="R106" t="n">
-        <v>6804539</v>
+        <v>6804598</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11277,7 +11276,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11287,7 +11286,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11296,6 +11295,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -11640,10 +11640,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132748983</v>
+        <v>132748975</v>
       </c>
       <c r="B110" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447651</v>
+        <v>447624</v>
       </c>
       <c r="R110" t="n">
-        <v>6804611</v>
+        <v>6804577</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11854,7 +11854,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132748975</v>
+        <v>132748963</v>
       </c>
       <c r="B112" t="n">
         <v>79333</v>
@@ -11889,10 +11889,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447624</v>
+        <v>447587</v>
       </c>
       <c r="R112" t="n">
-        <v>6804577</v>
+        <v>6804575</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11961,10 +11961,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748963</v>
+        <v>132748983</v>
       </c>
       <c r="B113" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11972,21 +11972,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447587</v>
+        <v>447651</v>
       </c>
       <c r="R113" t="n">
-        <v>6804575</v>
+        <v>6804611</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD113" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -10762,32 +10762,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>132748962</v>
+        <v>132748958</v>
       </c>
       <c r="B102" t="n">
-        <v>79419</v>
+        <v>79333</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10797,10 +10797,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447586</v>
+        <v>447602</v>
       </c>
       <c r="R102" t="n">
-        <v>6804596</v>
+        <v>6804649</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10869,32 +10869,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>132748958</v>
+        <v>132748962</v>
       </c>
       <c r="B103" t="n">
-        <v>79333</v>
+        <v>79419</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447602</v>
+        <v>447586</v>
       </c>
       <c r="R103" t="n">
-        <v>6804649</v>
+        <v>6804596</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10939,7 +10939,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11314,45 +11314,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>132748959</v>
+        <v>132748979</v>
       </c>
       <c r="B107" t="n">
-        <v>79333</v>
+        <v>5179</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447584</v>
+        <v>447677</v>
       </c>
       <c r="R107" t="n">
-        <v>6804624</v>
+        <v>6804549</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11384,7 +11389,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11394,7 +11399,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11421,50 +11426,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>132748979</v>
+        <v>132748959</v>
       </c>
       <c r="B108" t="n">
-        <v>5179</v>
+        <v>79333</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllen, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447677</v>
+        <v>447584</v>
       </c>
       <c r="R108" t="n">
-        <v>6804549</v>
+        <v>6804624</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11640,10 +11640,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>132748975</v>
+        <v>132748983</v>
       </c>
       <c r="B110" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11651,21 +11651,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11675,10 +11675,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447624</v>
+        <v>447651</v>
       </c>
       <c r="R110" t="n">
-        <v>6804577</v>
+        <v>6804611</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11747,32 +11747,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>132748970</v>
+        <v>132748963</v>
       </c>
       <c r="B111" t="n">
-        <v>79419</v>
+        <v>79333</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447609</v>
+        <v>447587</v>
       </c>
       <c r="R111" t="n">
-        <v>6804599</v>
+        <v>6804575</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11817,7 +11817,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11854,32 +11854,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>132748963</v>
+        <v>132748970</v>
       </c>
       <c r="B112" t="n">
-        <v>79333</v>
+        <v>79419</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11889,10 +11889,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447587</v>
+        <v>447609</v>
       </c>
       <c r="R112" t="n">
-        <v>6804575</v>
+        <v>6804599</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11924,7 +11924,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11961,10 +11961,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>132748983</v>
+        <v>132748975</v>
       </c>
       <c r="B113" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11972,21 +11972,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11996,10 +11996,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447651</v>
+        <v>447624</v>
       </c>
       <c r="R113" t="n">
-        <v>6804611</v>
+        <v>6804577</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12282,32 +12282,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132748974</v>
+        <v>132748968</v>
       </c>
       <c r="B116" t="n">
-        <v>79419</v>
+        <v>79333</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12317,10 +12317,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447619</v>
+        <v>447606</v>
       </c>
       <c r="R116" t="n">
-        <v>6804597</v>
+        <v>6804603</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12352,7 +12352,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12362,7 +12362,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12389,32 +12389,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>132748968</v>
+        <v>132748974</v>
       </c>
       <c r="B117" t="n">
-        <v>79333</v>
+        <v>79419</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12424,10 +12424,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447606</v>
+        <v>447619</v>
       </c>
       <c r="R117" t="n">
-        <v>6804603</v>
+        <v>6804597</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12469,7 +12469,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD117" t="b">

--- a/artfynd/A 55981-2025 artfynd.xlsx
+++ b/artfynd/A 55981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY145"/>
+  <dimension ref="A1:AZ145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748950</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748954</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748971</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748960</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748948</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748980</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748983</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748986</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748981</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893327</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893369</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1931,6 +1991,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893370</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2033,6 +2098,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893371</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2135,6 +2205,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893372</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893373</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2339,6 +2419,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893374</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,6 +2526,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893375</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2538,6 +2628,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893376</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2635,6 +2730,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893377</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2732,6 +2832,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893378</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2834,6 +2939,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893379</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2936,6 +3046,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893380</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3033,6 +3148,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893381</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3130,6 +3250,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893382</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3227,6 +3352,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893383</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3324,6 +3454,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893384</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3421,6 +3556,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893385</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3518,6 +3658,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893386</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3615,6 +3760,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893387</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3712,6 +3862,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893388</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3809,6 +3964,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893389</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3906,6 +4066,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893390</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4003,6 +4168,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893391</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4105,6 +4275,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893410</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4202,6 +4377,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893991</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4304,6 +4484,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893992</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4401,6 +4586,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893993</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4498,6 +4688,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893994</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4595,6 +4790,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893995</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4692,6 +4892,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893996</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4789,6 +4994,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893997</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4886,6 +5096,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893998</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4983,6 +5198,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893999</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5085,6 +5305,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894000</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5182,6 +5407,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894001</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5279,6 +5509,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894002</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5380,6 +5615,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894003</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5477,6 +5717,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894004</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5583,6 +5828,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894005</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5680,6 +5930,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894006</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5782,6 +6037,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894007</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5879,6 +6139,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894008</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5981,6 +6246,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894009</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6078,6 +6348,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894010</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6180,6 +6455,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894011</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6277,6 +6557,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894012</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6374,6 +6659,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894013</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6471,6 +6761,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894014</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6573,6 +6868,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894015</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6670,6 +6970,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894016</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6767,6 +7072,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894018</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6864,6 +7174,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894019</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6961,6 +7276,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894020</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7063,6 +7383,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894021</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7164,6 +7489,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894022</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7261,6 +7591,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894048</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7368,6 +7703,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748947</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7480,6 +7820,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748949</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7592,6 +7937,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748951</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7704,6 +8054,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748952</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7811,6 +8166,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748953</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7918,6 +8278,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748957</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8025,6 +8390,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748958</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8132,6 +8502,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748959</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8239,6 +8614,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748963</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8346,6 +8726,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748964</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8453,6 +8838,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748968</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8560,6 +8950,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748975</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8667,6 +9062,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748976</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8774,6 +9174,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748978</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8871,6 +9276,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132844424</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8968,6 +9378,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132844425</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9065,6 +9480,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132844417</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9162,6 +9582,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893966</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9281,6 +9706,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748961</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9388,6 +9818,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748962</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9495,6 +9930,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748965</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9602,6 +10042,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748966</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9709,6 +10154,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748967</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9816,6 +10266,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748969</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9923,6 +10378,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748970</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10030,6 +10490,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748972</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10137,6 +10602,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748974</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10234,6 +10704,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132844419</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10331,6 +10806,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132844420</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10428,6 +10908,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132844422</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10525,6 +11010,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893292</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10622,6 +11112,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893293</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10719,6 +11214,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893294</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10816,6 +11316,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893901</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10913,6 +11418,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893902</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11010,6 +11520,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893903</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11107,6 +11622,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893904</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11204,6 +11724,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893905</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11301,6 +11826,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893906</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11398,6 +11928,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893907</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11495,6 +12030,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893908</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11592,6 +12132,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893909</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11689,6 +12234,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893910</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11786,6 +12336,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893911</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11883,6 +12438,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893915</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11989,6 +12549,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893341</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12094,6 +12659,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893317</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12199,6 +12769,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893318</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12304,6 +12879,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893319</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12409,6 +12989,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893320</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12514,6 +13099,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893321</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12619,6 +13209,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893927</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12724,6 +13319,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893928</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12829,6 +13429,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893929</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12934,6 +13539,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893930</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13039,6 +13649,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893931</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13144,6 +13759,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893941</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13261,6 +13881,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748982</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13366,6 +13991,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893922</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13478,6 +14108,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748977</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13590,6 +14225,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748979</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13697,6 +14337,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893335</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13804,6 +14449,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893336</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13911,6 +14561,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893337</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14018,6 +14673,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893338</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14125,6 +14785,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893339</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14232,6 +14897,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893340</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14339,6 +15009,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893957</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14446,6 +15121,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893958</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14553,6 +15233,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893959</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14660,6 +15345,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893960</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14767,6 +15457,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893961</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14874,6 +15569,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893962</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14971,6 +15671,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893947</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15068,6 +15773,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893916</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15165,6 +15875,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893917</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15267,6 +15982,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748984</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15369,8 +16089,159 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132748985</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>